--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -632,22 +632,25 @@
         <v>43</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F3">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>86.05</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>13.95</v>
+      </c>
+      <c r="I3" s="2">
+        <v>7.3</v>
       </c>
       <c r="J3">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -664,22 +667,25 @@
         <v>39</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F4">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>74.36</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>25.64</v>
+      </c>
+      <c r="I4" s="2">
+        <v>6.2</v>
       </c>
       <c r="J4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -696,22 +702,25 @@
         <v>40</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -728,22 +737,25 @@
         <v>37</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>62.16</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>37.84</v>
+      </c>
+      <c r="I6" s="2">
+        <v>6.2</v>
       </c>
       <c r="J6">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -760,22 +772,25 @@
         <v>41</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>78.05</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>21.95</v>
+      </c>
+      <c r="I7" s="2">
+        <v>6.8</v>
       </c>
       <c r="J7">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -792,22 +807,25 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>48.39</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>51.61</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5.8</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -824,22 +842,25 @@
         <v>42</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>59.52</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>40.48</v>
+      </c>
+      <c r="I9" s="2">
+        <v>6.3</v>
       </c>
       <c r="J9">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -856,22 +877,25 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>74.19</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>25.81</v>
+      </c>
+      <c r="I10" s="2">
+        <v>6.1</v>
       </c>
       <c r="J10">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -888,22 +912,25 @@
         <v>38</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F11">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>92.11</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>7.89</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.3</v>
       </c>
       <c r="J11">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -920,22 +947,25 @@
         <v>28</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>35.71</v>
+      </c>
+      <c r="I12" s="2">
+        <v>5.9</v>
       </c>
       <c r="J12">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -952,22 +982,25 @@
         <v>41</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>31.71</v>
+      </c>
+      <c r="I13" s="2">
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -984,22 +1017,25 @@
         <v>32</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I14" s="2">
+        <v>6.5</v>
       </c>
       <c r="J14">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1016,22 +1052,25 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>7.3</v>
       </c>
       <c r="J15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1048,22 +1087,25 @@
         <v>30</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F16">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>76.67</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>23.33</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7.6</v>
       </c>
       <c r="J16">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1115,22 +1157,25 @@
         <v>20</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1159,13 +1204,13 @@
         <v>10</v>
       </c>
       <c r="I19" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1214,22 +1259,25 @@
         <v>28</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F21">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>7.1</v>
       </c>
       <c r="J21">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1281,22 +1329,25 @@
         <v>32</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F23">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>3.13</v>
+      </c>
+      <c r="I23" s="2">
+        <v>8.6</v>
       </c>
       <c r="J23">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1313,22 +1364,25 @@
         <v>21</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F24">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>33.33</v>
+      </c>
+      <c r="I24" s="2">
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1345,22 +1399,25 @@
         <v>31</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F25">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>93.55</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>6.45</v>
+      </c>
+      <c r="I25" s="2">
+        <v>7.9</v>
       </c>
       <c r="J25">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -3277,22 +3334,25 @@
         <v>43</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F3">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>86.05</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>13.95</v>
+      </c>
+      <c r="I3" s="2">
+        <v>7.3</v>
       </c>
       <c r="J3">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3309,22 +3369,25 @@
         <v>39</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F4">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>74.36</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>25.64</v>
+      </c>
+      <c r="I4" s="2">
+        <v>6.5</v>
       </c>
       <c r="J4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3341,22 +3404,25 @@
         <v>40</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3373,22 +3439,25 @@
         <v>37</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>62.16</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>37.84</v>
+      </c>
+      <c r="I6" s="2">
+        <v>6.2</v>
       </c>
       <c r="J6">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3405,22 +3474,25 @@
         <v>41</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>78.05</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>21.95</v>
+      </c>
+      <c r="I7" s="2">
+        <v>6.8</v>
       </c>
       <c r="J7">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3437,22 +3509,25 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>48.39</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>51.61</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5.8</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3469,22 +3544,25 @@
         <v>42</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>59.52</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>40.48</v>
+      </c>
+      <c r="I9" s="2">
+        <v>6.3</v>
       </c>
       <c r="J9">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3501,22 +3579,25 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>74.19</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>25.81</v>
+      </c>
+      <c r="I10" s="2">
+        <v>6.1</v>
       </c>
       <c r="J10">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -3533,22 +3614,25 @@
         <v>38</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F11">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>92.11</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>7.89</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.3</v>
       </c>
       <c r="J11">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -3565,22 +3649,25 @@
         <v>28</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>35.71</v>
+      </c>
+      <c r="I12" s="2">
+        <v>5.9</v>
       </c>
       <c r="J12">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3597,22 +3684,25 @@
         <v>41</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>31.71</v>
+      </c>
+      <c r="I13" s="2">
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3629,22 +3719,25 @@
         <v>32</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I14" s="2">
+        <v>6.7</v>
       </c>
       <c r="J14">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -3661,22 +3754,25 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>7.3</v>
       </c>
       <c r="J15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3693,22 +3789,25 @@
         <v>30</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F16">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>76.67</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>23.33</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7.7</v>
       </c>
       <c r="J16">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -3760,22 +3859,25 @@
         <v>20</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3804,13 +3906,13 @@
         <v>10</v>
       </c>
       <c r="I19" s="2">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3859,22 +3961,25 @@
         <v>28</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F21">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>7.1</v>
       </c>
       <c r="J21">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -3926,22 +4031,25 @@
         <v>32</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F23">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>3.13</v>
+      </c>
+      <c r="I23" s="2">
+        <v>8.6</v>
       </c>
       <c r="J23">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -3958,22 +4066,25 @@
         <v>21</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F24">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>33.33</v>
+      </c>
+      <c r="I24" s="2">
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3990,22 +4101,25 @@
         <v>31</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F25">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>93.55</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>6.45</v>
+      </c>
+      <c r="I25" s="2">
+        <v>7.9</v>
       </c>
       <c r="J25">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="26" spans="1:11">

--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -600,22 +600,25 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>11.76</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.3</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1227,22 +1230,25 @@
         <v>36</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F20">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1329,25 +1335,25 @@
         <v>32</v>
       </c>
       <c r="E23">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1399,25 +1405,25 @@
         <v>31</v>
       </c>
       <c r="E25">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -3302,22 +3308,25 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>11.76</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.3</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -3929,22 +3938,25 @@
         <v>36</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F20">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4031,25 +4043,25 @@
         <v>32</v>
       </c>
       <c r="E23">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4101,25 +4113,25 @@
         <v>31</v>
       </c>
       <c r="E25">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">

--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -1860,22 +1860,25 @@
         <v>30</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F38">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>36.67</v>
       </c>
       <c r="H38" s="1">
-        <v>100</v>
+        <v>63.33</v>
+      </c>
+      <c r="I38" s="2">
+        <v>5</v>
       </c>
       <c r="J38">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -1892,22 +1895,25 @@
         <v>33</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F39">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H39" s="1">
-        <v>100</v>
+        <v>33.33</v>
+      </c>
+      <c r="I39" s="2">
+        <v>6.8</v>
       </c>
       <c r="J39">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -1924,22 +1930,25 @@
         <v>33</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F40">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>54.55</v>
       </c>
       <c r="H40" s="1">
-        <v>100</v>
+        <v>45.45</v>
+      </c>
+      <c r="I40" s="2">
+        <v>5.8</v>
       </c>
       <c r="J40">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4568,22 +4577,25 @@
         <v>30</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F38">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>36.67</v>
       </c>
       <c r="H38" s="1">
-        <v>100</v>
+        <v>63.33</v>
+      </c>
+      <c r="I38" s="2">
+        <v>5.6</v>
       </c>
       <c r="J38">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -4600,22 +4612,25 @@
         <v>33</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F39">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H39" s="1">
-        <v>100</v>
+        <v>33.33</v>
+      </c>
+      <c r="I39" s="2">
+        <v>6.9</v>
       </c>
       <c r="J39">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -4632,22 +4647,25 @@
         <v>33</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F40">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>54.55</v>
       </c>
       <c r="H40" s="1">
-        <v>100</v>
+        <v>45.45</v>
+      </c>
+      <c r="I40" s="2">
+        <v>6.1</v>
       </c>
       <c r="J40">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -1472,28 +1472,28 @@
         <v>51</v>
       </c>
       <c r="D27">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E27">
         <v>12</v>
       </c>
       <c r="F27">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G27" s="1">
-        <v>41.38</v>
+        <v>40</v>
       </c>
       <c r="H27" s="1">
-        <v>58.62</v>
+        <v>60</v>
       </c>
       <c r="I27" s="2">
         <v>6</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1647,28 +1647,28 @@
         <v>51</v>
       </c>
       <c r="D32">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E32">
         <v>25</v>
       </c>
       <c r="F32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G32" s="1">
-        <v>75.76000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="H32" s="1">
-        <v>24.24</v>
+        <v>26.47</v>
       </c>
       <c r="I32" s="2">
         <v>6.9</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2814,13 +2814,13 @@
         <v>51</v>
       </c>
       <c r="D27">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K27" s="1">
         <v>100</v>
@@ -2974,13 +2974,13 @@
         <v>51</v>
       </c>
       <c r="D32">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -4189,28 +4189,28 @@
         <v>51</v>
       </c>
       <c r="D27">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E27">
         <v>12</v>
       </c>
       <c r="F27">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G27" s="1">
-        <v>41.38</v>
+        <v>40</v>
       </c>
       <c r="H27" s="1">
-        <v>58.62</v>
+        <v>60</v>
       </c>
       <c r="I27" s="2">
         <v>6.1</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -4364,28 +4364,28 @@
         <v>51</v>
       </c>
       <c r="D32">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E32">
         <v>25</v>
       </c>
       <c r="F32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G32" s="1">
-        <v>75.76000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="H32" s="1">
-        <v>24.24</v>
+        <v>26.47</v>
       </c>
       <c r="I32" s="2">
         <v>6.8</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="33" spans="1:11">

--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="59">
   <si>
     <t>Docente</t>
   </si>
@@ -51,114 +51,129 @@
     <t>Por_Blan</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
-  </si>
-  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
     <t>Santiago Hernández Mariana</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>4APM</t>
+  </si>
+  <si>
+    <t>4ARHV</t>
+  </si>
+  <si>
+    <t>6ALCV</t>
+  </si>
+  <si>
+    <t>6APV</t>
+  </si>
+  <si>
+    <t>6ASV</t>
+  </si>
+  <si>
+    <t>2BEM</t>
+  </si>
+  <si>
+    <t>2AEV</t>
+  </si>
+  <si>
+    <t>2ALCV</t>
+  </si>
+  <si>
+    <t>4AEM</t>
+  </si>
+  <si>
+    <t>4ARHM</t>
+  </si>
+  <si>
+    <t>4BEM</t>
+  </si>
+  <si>
+    <t>4BLCM</t>
+  </si>
+  <si>
+    <t>2APM</t>
+  </si>
+  <si>
+    <t>6ARHM</t>
+  </si>
+  <si>
+    <t>6BLCM</t>
+  </si>
+  <si>
+    <t>6AEV</t>
+  </si>
+  <si>
+    <t>6ARHV</t>
+  </si>
+  <si>
+    <t>6AEM</t>
+  </si>
+  <si>
+    <t>6APM</t>
+  </si>
+  <si>
+    <t>6BEM</t>
+  </si>
+  <si>
+    <t>4ALCM</t>
+  </si>
+  <si>
+    <t>4ALCV</t>
+  </si>
+  <si>
+    <t>4APV</t>
+  </si>
+  <si>
+    <t>4ASV</t>
+  </si>
+  <si>
     <t>2AEM</t>
   </si>
   <si>
     <t>2ALCM</t>
   </si>
   <si>
-    <t>2APM</t>
-  </si>
-  <si>
     <t>2ARHM</t>
   </si>
   <si>
-    <t>2BEM</t>
-  </si>
-  <si>
     <t>2BLCM</t>
   </si>
   <si>
-    <t>2AEV</t>
-  </si>
-  <si>
-    <t>2ALCV</t>
-  </si>
-  <si>
-    <t>4AEM</t>
-  </si>
-  <si>
-    <t>4ARHM</t>
-  </si>
-  <si>
-    <t>4BEM</t>
-  </si>
-  <si>
-    <t>4BLCM</t>
-  </si>
-  <si>
     <t>4AEV</t>
   </si>
   <si>
-    <t>6AEM</t>
-  </si>
-  <si>
     <t>6ALCM</t>
   </si>
   <si>
-    <t>6APM</t>
-  </si>
-  <si>
-    <t>6ARHM</t>
-  </si>
-  <si>
-    <t>6BEM</t>
-  </si>
-  <si>
-    <t>6BLCM</t>
-  </si>
-  <si>
-    <t>6AEV</t>
-  </si>
-  <si>
-    <t>6ARHV</t>
-  </si>
-  <si>
-    <t>4APM</t>
-  </si>
-  <si>
-    <t>4ARHV</t>
-  </si>
-  <si>
-    <t>6ALCV</t>
-  </si>
-  <si>
-    <t>6APV</t>
-  </si>
-  <si>
-    <t>6ASV</t>
-  </si>
-  <si>
-    <t>4ALCM</t>
-  </si>
-  <si>
-    <t>4ALCV</t>
-  </si>
-  <si>
-    <t>4APV</t>
-  </si>
-  <si>
-    <t>4ASV</t>
-  </si>
-  <si>
     <t>2APV</t>
   </si>
   <si>
@@ -168,16 +183,16 @@
     <t>2ASV</t>
   </si>
   <si>
+    <t>CÁLCULO DIFERENCIAL</t>
+  </si>
+  <si>
+    <t>PROBABILIDAD Y ESTADÍSTICA</t>
+  </si>
+  <si>
     <t>GEOMETRÍA Y TRIGONOMETRÍA</t>
   </si>
   <si>
-    <t>CÁLCULO DIFERENCIAL</t>
-  </si>
-  <si>
     <t>MATEMÁTICAS APLICADAS</t>
-  </si>
-  <si>
-    <t>PROBABILIDAD Y ESTADÍSTICA</t>
   </si>
 </sst>
 </file>
@@ -591,28 +606,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1">
-        <v>88.23999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="H2" s="1">
-        <v>11.76</v>
+        <v>33.33</v>
       </c>
       <c r="I2" s="2">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -626,34 +641,34 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
+      </c>
+      <c r="E3">
+        <v>12</v>
+      </c>
+      <c r="F3">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3">
-        <v>43</v>
-      </c>
-      <c r="E3">
-        <v>37</v>
-      </c>
-      <c r="F3">
+      <c r="G3" s="1">
+        <v>40</v>
+      </c>
+      <c r="H3" s="1">
+        <v>60</v>
+      </c>
+      <c r="I3" s="2">
         <v>6</v>
       </c>
-      <c r="G3" s="1">
-        <v>86.05</v>
-      </c>
-      <c r="H3" s="1">
-        <v>13.95</v>
-      </c>
-      <c r="I3" s="2">
-        <v>7.3</v>
-      </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -661,28 +676,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>74.36</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>25.64</v>
+        <v>11.54</v>
       </c>
       <c r="I4" s="2">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -696,28 +711,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="I5" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -731,28 +746,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>62.16</v>
+        <v>89.47</v>
       </c>
       <c r="H6" s="1">
-        <v>37.84</v>
+        <v>10.53</v>
       </c>
       <c r="I6" s="2">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -763,31 +778,31 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1">
-        <v>78.05</v>
+        <v>62.16</v>
       </c>
       <c r="H7" s="1">
-        <v>21.95</v>
+        <v>37.84</v>
       </c>
       <c r="I7" s="2">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -798,13 +813,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D8">
         <v>31</v>
@@ -833,13 +848,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D9">
         <v>42</v>
@@ -868,13 +883,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D10">
         <v>31</v>
@@ -903,13 +918,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D11">
         <v>38</v>
@@ -938,13 +953,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D12">
         <v>28</v>
@@ -973,13 +988,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D13">
         <v>41</v>
@@ -1008,31 +1023,31 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14">
+        <v>39</v>
+      </c>
+      <c r="E14">
         <v>29</v>
       </c>
-      <c r="C14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14">
-        <v>32</v>
-      </c>
-      <c r="E14">
-        <v>24</v>
-      </c>
       <c r="F14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G14" s="1">
-        <v>75</v>
+        <v>74.36</v>
       </c>
       <c r="H14" s="1">
-        <v>25</v>
+        <v>25.64</v>
       </c>
       <c r="I14" s="2">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1043,31 +1058,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D15">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E15">
         <v>30</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="I15" s="2">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1078,31 +1093,31 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E16">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>76.67</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>23.33</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1113,31 +1128,31 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D17">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E17">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G17" s="1">
-        <v>91.18000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="H17" s="1">
-        <v>8.82</v>
+        <v>33.33</v>
       </c>
       <c r="I17" s="2">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1148,19 +1163,19 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D18">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1172,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1183,31 +1198,31 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E19">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1218,31 +1233,31 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D20">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E20">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1253,13 +1268,13 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D21">
         <v>28</v>
@@ -1288,31 +1303,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D22">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E22">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F22">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G22" s="1">
-        <v>71.43000000000001</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>28.57</v>
+        <v>9.76</v>
       </c>
       <c r="I22" s="2">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -1323,66 +1338,66 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D23">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E23">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G23" s="1">
-        <v>100</v>
+        <v>73.53</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>26.47</v>
       </c>
       <c r="I23" s="2">
-        <v>8.5</v>
+        <v>6.9</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D24">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E24">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G24" s="1">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="H24" s="1">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="I24" s="2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -1393,31 +1408,31 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D25">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="E25">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G25" s="1">
-        <v>100</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>28.57</v>
       </c>
       <c r="I25" s="2">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1428,31 +1443,31 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D26">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E26">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F26">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G26" s="1">
-        <v>66.67</v>
+        <v>47.62</v>
       </c>
       <c r="H26" s="1">
-        <v>33.33</v>
+        <v>52.38</v>
       </c>
       <c r="I26" s="2">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1463,66 +1478,66 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D27">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F27">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G27" s="1">
-        <v>40</v>
+        <v>78.95</v>
       </c>
       <c r="H27" s="1">
-        <v>60</v>
+        <v>21.05</v>
       </c>
       <c r="I27" s="2">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D28">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E28">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="1">
-        <v>88.45999999999999</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H28" s="1">
-        <v>11.54</v>
+        <v>11.76</v>
       </c>
       <c r="I28" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -1533,31 +1548,31 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D29">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="E29">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G29" s="1">
-        <v>88.23999999999999</v>
+        <v>86.05</v>
       </c>
       <c r="H29" s="1">
-        <v>11.76</v>
+        <v>13.95</v>
       </c>
       <c r="I29" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1568,31 +1583,31 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D30">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E30">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G30" s="1">
-        <v>89.47</v>
+        <v>87.5</v>
       </c>
       <c r="H30" s="1">
-        <v>10.53</v>
+        <v>12.5</v>
       </c>
       <c r="I30" s="2">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -1603,31 +1618,31 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D31">
         <v>41</v>
       </c>
       <c r="E31">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G31" s="1">
-        <v>90.23999999999999</v>
+        <v>78.05</v>
       </c>
       <c r="H31" s="1">
-        <v>9.76</v>
+        <v>21.95</v>
       </c>
       <c r="I31" s="2">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -1638,66 +1653,66 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D32">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E32">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F32">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>73.53</v>
+        <v>100</v>
       </c>
       <c r="H32" s="1">
-        <v>26.47</v>
+        <v>0</v>
       </c>
       <c r="I32" s="2">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D33">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E33">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F33">
         <v>8</v>
       </c>
       <c r="G33" s="1">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H33" s="1">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I33" s="2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -1708,31 +1723,31 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D34">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F34">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G34" s="1">
-        <v>71.43000000000001</v>
+        <v>76.67</v>
       </c>
       <c r="H34" s="1">
-        <v>28.57</v>
+        <v>23.33</v>
       </c>
       <c r="I34" s="2">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -1743,31 +1758,31 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D35">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E35">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F35">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G35" s="1">
-        <v>47.62</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H35" s="1">
-        <v>52.38</v>
+        <v>8.82</v>
       </c>
       <c r="I35" s="2">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -1778,31 +1793,31 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D36">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E36">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G36" s="1">
-        <v>78.95</v>
+        <v>90</v>
       </c>
       <c r="H36" s="1">
-        <v>21.05</v>
+        <v>10</v>
       </c>
       <c r="I36" s="2">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -1813,31 +1828,31 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B37" t="s">
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D37">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E37">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G37" s="1">
-        <v>100</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <v>28.57</v>
       </c>
       <c r="I37" s="2">
-        <v>9.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -1848,13 +1863,13 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D38">
         <v>30</v>
@@ -1883,13 +1898,13 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D39">
         <v>33</v>
@@ -1918,13 +1933,13 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D40">
         <v>33</v>
@@ -2008,19 +2023,19 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -2029,7 +2044,7 @@
         <v>100</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K2" s="1">
         <v>100</v>
@@ -2040,19 +2055,19 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -2061,7 +2076,7 @@
         <v>100</v>
       </c>
       <c r="J3">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="K3" s="1">
         <v>100</v>
@@ -2072,19 +2087,19 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -2093,7 +2108,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="K4" s="1">
         <v>100</v>
@@ -2104,19 +2119,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -2125,7 +2140,7 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="K5" s="1">
         <v>100</v>
@@ -2136,19 +2151,19 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -2157,7 +2172,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -2165,22 +2180,22 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -2189,7 +2204,7 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -2197,13 +2212,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D8">
         <v>31</v>
@@ -2229,13 +2244,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D9">
         <v>42</v>
@@ -2261,13 +2276,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D10">
         <v>31</v>
@@ -2293,13 +2308,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D11">
         <v>38</v>
@@ -2325,13 +2340,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D12">
         <v>28</v>
@@ -2357,13 +2372,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D13">
         <v>41</v>
@@ -2389,22 +2404,22 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D14">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -2413,7 +2428,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -2421,22 +2436,22 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D15">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -2445,7 +2460,7 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -2453,22 +2468,22 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -2477,7 +2492,7 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -2485,22 +2500,22 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D17">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -2509,7 +2524,7 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -2517,22 +2532,22 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D18">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -2541,7 +2556,7 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="K18" s="1">
         <v>100</v>
@@ -2549,22 +2564,22 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -2573,7 +2588,7 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K19" s="1">
         <v>100</v>
@@ -2581,22 +2596,22 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D20">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -2605,7 +2620,7 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="K20" s="1">
         <v>100</v>
@@ -2613,13 +2628,13 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D21">
         <v>28</v>
@@ -2645,22 +2660,22 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D22">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
@@ -2669,7 +2684,7 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="K22" s="1">
         <v>100</v>
@@ -2677,22 +2692,22 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D23">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
@@ -2701,7 +2716,7 @@
         <v>100</v>
       </c>
       <c r="J23">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K23" s="1">
         <v>100</v>
@@ -2709,22 +2724,22 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D24">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
@@ -2733,7 +2748,7 @@
         <v>100</v>
       </c>
       <c r="J24">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K24" s="1">
         <v>100</v>
@@ -2741,22 +2756,22 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D25">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
@@ -2765,7 +2780,7 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="K25" s="1">
         <v>100</v>
@@ -2773,22 +2788,22 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D26">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
@@ -2797,7 +2812,7 @@
         <v>100</v>
       </c>
       <c r="J26">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -2805,22 +2820,22 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D27">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
@@ -2829,7 +2844,7 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="K27" s="1">
         <v>100</v>
@@ -2837,22 +2852,22 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D28">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
@@ -2861,7 +2876,7 @@
         <v>100</v>
       </c>
       <c r="J28">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K28" s="1">
         <v>100</v>
@@ -2869,22 +2884,22 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D29">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
@@ -2893,7 +2908,7 @@
         <v>100</v>
       </c>
       <c r="J29">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="K29" s="1">
         <v>100</v>
@@ -2901,22 +2916,22 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D30">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
@@ -2925,7 +2940,7 @@
         <v>100</v>
       </c>
       <c r="J30">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="K30" s="1">
         <v>100</v>
@@ -2933,13 +2948,13 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D31">
         <v>41</v>
@@ -2965,22 +2980,22 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D32">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
@@ -2989,7 +3004,7 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -2997,22 +3012,22 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D33">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
@@ -3021,7 +3036,7 @@
         <v>100</v>
       </c>
       <c r="J33">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -3029,22 +3044,22 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D34">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
@@ -3053,7 +3068,7 @@
         <v>100</v>
       </c>
       <c r="J34">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -3061,22 +3076,22 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D35">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
@@ -3085,7 +3100,7 @@
         <v>100</v>
       </c>
       <c r="J35">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K35" s="1">
         <v>100</v>
@@ -3093,22 +3108,22 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D36">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E36">
         <v>0</v>
       </c>
       <c r="F36">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
@@ -3117,7 +3132,7 @@
         <v>100</v>
       </c>
       <c r="J36">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -3125,22 +3140,22 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B37" t="s">
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D37">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G37" s="1">
         <v>0</v>
@@ -3149,7 +3164,7 @@
         <v>100</v>
       </c>
       <c r="J37">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="K37" s="1">
         <v>100</v>
@@ -3157,13 +3172,13 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D38">
         <v>30</v>
@@ -3189,13 +3204,13 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D39">
         <v>33</v>
@@ -3221,13 +3236,13 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D40">
         <v>33</v>
@@ -3308,28 +3323,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1">
-        <v>88.23999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="H2" s="1">
-        <v>11.76</v>
+        <v>33.33</v>
       </c>
       <c r="I2" s="2">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3343,34 +3358,34 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
+      </c>
+      <c r="E3">
+        <v>12</v>
+      </c>
+      <c r="F3">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3">
-        <v>43</v>
-      </c>
-      <c r="E3">
-        <v>37</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
       <c r="G3" s="1">
-        <v>86.05</v>
+        <v>40</v>
       </c>
       <c r="H3" s="1">
-        <v>13.95</v>
+        <v>60</v>
       </c>
       <c r="I3" s="2">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3378,28 +3393,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>74.36</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>25.64</v>
+        <v>11.54</v>
       </c>
       <c r="I4" s="2">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3413,28 +3428,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="I5" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3448,28 +3463,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>62.16</v>
+        <v>89.47</v>
       </c>
       <c r="H6" s="1">
-        <v>37.84</v>
+        <v>10.53</v>
       </c>
       <c r="I6" s="2">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3480,31 +3495,31 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1">
-        <v>78.05</v>
+        <v>62.16</v>
       </c>
       <c r="H7" s="1">
-        <v>21.95</v>
+        <v>37.84</v>
       </c>
       <c r="I7" s="2">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3515,13 +3530,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D8">
         <v>31</v>
@@ -3550,13 +3565,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D9">
         <v>42</v>
@@ -3585,13 +3600,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D10">
         <v>31</v>
@@ -3620,13 +3635,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D11">
         <v>38</v>
@@ -3655,13 +3670,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D12">
         <v>28</v>
@@ -3690,13 +3705,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D13">
         <v>41</v>
@@ -3725,31 +3740,31 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14">
+        <v>39</v>
+      </c>
+      <c r="E14">
         <v>29</v>
       </c>
-      <c r="C14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14">
-        <v>32</v>
-      </c>
-      <c r="E14">
-        <v>24</v>
-      </c>
       <c r="F14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G14" s="1">
-        <v>75</v>
+        <v>74.36</v>
       </c>
       <c r="H14" s="1">
-        <v>25</v>
+        <v>25.64</v>
       </c>
       <c r="I14" s="2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3760,31 +3775,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D15">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E15">
         <v>30</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="I15" s="2">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3795,31 +3810,31 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E16">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>76.67</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>23.33</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3830,31 +3845,31 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D17">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E17">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G17" s="1">
-        <v>91.18000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="H17" s="1">
-        <v>8.82</v>
+        <v>33.33</v>
       </c>
       <c r="I17" s="2">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3865,19 +3880,19 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D18">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E18">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -3889,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3900,28 +3915,28 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E19">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
         <v>7.3</v>
@@ -3935,31 +3950,31 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D20">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E20">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3970,13 +3985,13 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D21">
         <v>28</v>
@@ -4005,31 +4020,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D22">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E22">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F22">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G22" s="1">
-        <v>71.43000000000001</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>28.57</v>
+        <v>9.76</v>
       </c>
       <c r="I22" s="2">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4040,66 +4055,66 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D23">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E23">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G23" s="1">
-        <v>100</v>
+        <v>73.53</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>26.47</v>
       </c>
       <c r="I23" s="2">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D24">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E24">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G24" s="1">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="H24" s="1">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="I24" s="2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -4110,31 +4125,31 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D25">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="E25">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G25" s="1">
-        <v>100</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>28.57</v>
       </c>
       <c r="I25" s="2">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4145,31 +4160,31 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D26">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E26">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F26">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G26" s="1">
-        <v>66.67</v>
+        <v>47.62</v>
       </c>
       <c r="H26" s="1">
-        <v>33.33</v>
+        <v>52.38</v>
       </c>
       <c r="I26" s="2">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4180,66 +4195,66 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D27">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F27">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G27" s="1">
-        <v>40</v>
+        <v>78.95</v>
       </c>
       <c r="H27" s="1">
-        <v>60</v>
+        <v>21.05</v>
       </c>
       <c r="I27" s="2">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D28">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E28">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="1">
-        <v>88.45999999999999</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H28" s="1">
-        <v>11.54</v>
+        <v>11.76</v>
       </c>
       <c r="I28" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4250,31 +4265,31 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D29">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="E29">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G29" s="1">
-        <v>88.23999999999999</v>
+        <v>86.05</v>
       </c>
       <c r="H29" s="1">
-        <v>11.76</v>
+        <v>13.95</v>
       </c>
       <c r="I29" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4285,31 +4300,31 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D30">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E30">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G30" s="1">
-        <v>89.47</v>
+        <v>87.5</v>
       </c>
       <c r="H30" s="1">
-        <v>10.53</v>
+        <v>12.5</v>
       </c>
       <c r="I30" s="2">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4320,31 +4335,31 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D31">
         <v>41</v>
       </c>
       <c r="E31">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G31" s="1">
-        <v>90.23999999999999</v>
+        <v>78.05</v>
       </c>
       <c r="H31" s="1">
-        <v>9.76</v>
+        <v>21.95</v>
       </c>
       <c r="I31" s="2">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4355,66 +4370,66 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D32">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E32">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F32">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>73.53</v>
+        <v>100</v>
       </c>
       <c r="H32" s="1">
-        <v>26.47</v>
+        <v>0</v>
       </c>
       <c r="I32" s="2">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D33">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E33">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F33">
         <v>8</v>
       </c>
       <c r="G33" s="1">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H33" s="1">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I33" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4425,31 +4440,31 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D34">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F34">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G34" s="1">
-        <v>71.43000000000001</v>
+        <v>76.67</v>
       </c>
       <c r="H34" s="1">
-        <v>28.57</v>
+        <v>23.33</v>
       </c>
       <c r="I34" s="2">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -4460,31 +4475,31 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D35">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E35">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F35">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G35" s="1">
-        <v>47.62</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H35" s="1">
-        <v>52.38</v>
+        <v>8.82</v>
       </c>
       <c r="I35" s="2">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4495,31 +4510,31 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D36">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E36">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G36" s="1">
-        <v>78.95</v>
+        <v>90</v>
       </c>
       <c r="H36" s="1">
-        <v>21.05</v>
+        <v>10</v>
       </c>
       <c r="I36" s="2">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -4530,31 +4545,31 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B37" t="s">
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D37">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E37">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G37" s="1">
-        <v>100</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <v>28.57</v>
       </c>
       <c r="I37" s="2">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -4565,13 +4580,13 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D38">
         <v>30</v>
@@ -4600,13 +4615,13 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D39">
         <v>33</v>
@@ -4635,13 +4650,13 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D40">
         <v>33</v>

--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -8,25 +8,24 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="Final" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="60">
   <si>
     <t>Docente</t>
   </si>
   <si>
+    <t>Mat</t>
+  </si>
+  <si>
     <t>Grupo</t>
   </si>
   <si>
-    <t>Mat</t>
-  </si>
-  <si>
     <t>Totales</t>
   </si>
   <si>
@@ -36,10 +35,10 @@
     <t>Reprobados</t>
   </si>
   <si>
-    <t>Por_Apro</t>
-  </si>
-  <si>
-    <t>Por_Repro</t>
+    <t>por_aprobados</t>
+  </si>
+  <si>
+    <t>por_reprobados</t>
   </si>
   <si>
     <t>Promedio</t>
@@ -48,7 +47,7 @@
     <t>Blancos</t>
   </si>
   <si>
-    <t>Por_Blan</t>
+    <t>por_blancos</t>
   </si>
   <si>
     <t>Domínguez Burgos Marioscar</t>
@@ -78,12 +77,27 @@
     <t>Santiago Hernández Mariana</t>
   </si>
   <si>
+    <t>Total</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>CÁLCULO DIFERENCIAL</t>
+  </si>
+  <si>
+    <t>PROBABILIDAD Y ESTADÍSTICA</t>
+  </si>
+  <si>
+    <t>GEOMETRÍA Y TRIGONOMETRÍA</t>
+  </si>
+  <si>
+    <t>MATEMÁTICAS APLICADAS</t>
+  </si>
+  <si>
     <t>4APM</t>
   </si>
   <si>
@@ -181,18 +195,6 @@
   </si>
   <si>
     <t>2ASV</t>
-  </si>
-  <si>
-    <t>CÁLCULO DIFERENCIAL</t>
-  </si>
-  <si>
-    <t>PROBABILIDAD Y ESTADÍSTICA</t>
-  </si>
-  <si>
-    <t>GEOMETRÍA Y TRIGONOMETRÍA</t>
-  </si>
-  <si>
-    <t>MATEMÁTICAS APLICADAS</t>
   </si>
 </sst>
 </file>
@@ -556,11 +558,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -606,10 +608,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="D2">
         <v>27</v>
@@ -621,10 +623,10 @@
         <v>9</v>
       </c>
       <c r="G2" s="1">
-        <v>66.67</v>
+        <v>66.7</v>
       </c>
       <c r="H2" s="1">
-        <v>33.33</v>
+        <v>33.3</v>
       </c>
       <c r="I2" s="2">
         <v>6.7</v>
@@ -644,7 +646,7 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>30</v>
@@ -679,7 +681,7 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>26</v>
@@ -691,10 +693,10 @@
         <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>88.45999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="H4" s="1">
-        <v>11.54</v>
+        <v>11.5</v>
       </c>
       <c r="I4" s="2">
         <v>7.6</v>
@@ -711,10 +713,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="D5">
         <v>17</v>
@@ -726,10 +728,10 @@
         <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>88.23999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="H5" s="1">
-        <v>11.76</v>
+        <v>11.8</v>
       </c>
       <c r="I5" s="2">
         <v>7.1</v>
@@ -746,10 +748,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D6">
         <v>19</v>
@@ -761,10 +763,10 @@
         <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>89.47</v>
+        <v>89.5</v>
       </c>
       <c r="H6" s="1">
-        <v>10.53</v>
+        <v>10.5</v>
       </c>
       <c r="I6" s="2">
         <v>7.3</v>
@@ -778,37 +780,31 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G7" s="1">
-        <v>62.16</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>37.84</v>
+        <v>28.6</v>
       </c>
       <c r="I7" s="2">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -816,28 +812,28 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1">
-        <v>48.39</v>
+        <v>62.2</v>
       </c>
       <c r="H8" s="1">
-        <v>51.61</v>
+        <v>37.8</v>
       </c>
       <c r="I8" s="2">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -851,28 +847,28 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D9">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1">
-        <v>59.52</v>
+        <v>48.4</v>
       </c>
       <c r="H9" s="1">
-        <v>40.48</v>
+        <v>51.6</v>
       </c>
       <c r="I9" s="2">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -886,28 +882,28 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="D10">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1">
-        <v>74.19</v>
+        <v>58.5</v>
       </c>
       <c r="H10" s="1">
-        <v>25.81</v>
+        <v>41.5</v>
       </c>
       <c r="I10" s="2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -921,28 +917,28 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11">
         <v>31</v>
       </c>
-      <c r="C11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11">
-        <v>38</v>
-      </c>
       <c r="E11">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>92.11</v>
+        <v>74.2</v>
       </c>
       <c r="H11" s="1">
-        <v>7.89</v>
+        <v>25.8</v>
       </c>
       <c r="I11" s="2">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -956,28 +952,28 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D12">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E12">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>64.29000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>35.71</v>
+        <v>7.9</v>
       </c>
       <c r="I12" s="2">
-        <v>5.9</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -991,28 +987,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="D13">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E13">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F13">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>68.29000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="H13" s="1">
-        <v>31.71</v>
+        <v>35.7</v>
       </c>
       <c r="I13" s="2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1023,31 +1019,31 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14">
+        <v>41</v>
+      </c>
+      <c r="E14">
+        <v>28</v>
+      </c>
+      <c r="F14">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14">
-        <v>39</v>
-      </c>
-      <c r="E14">
-        <v>29</v>
-      </c>
-      <c r="F14">
-        <v>10</v>
-      </c>
       <c r="G14" s="1">
-        <v>74.36</v>
+        <v>68.3</v>
       </c>
       <c r="H14" s="1">
-        <v>25.64</v>
+        <v>31.7</v>
       </c>
       <c r="I14" s="2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1058,31 +1054,25 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="D15">
-        <v>36</v>
+        <v>247</v>
       </c>
       <c r="E15">
-        <v>30</v>
+        <v>166</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="G15" s="1">
-        <v>83.33</v>
+        <v>67.2</v>
       </c>
       <c r="H15" s="1">
-        <v>16.67</v>
+        <v>32.8</v>
       </c>
       <c r="I15" s="2">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1093,31 +1083,31 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D16">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E16">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G16" s="1">
-        <v>100</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="I16" s="2">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1128,31 +1118,25 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D17">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E17">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1">
-        <v>66.67</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>33.33</v>
+        <v>25.6</v>
       </c>
       <c r="I17" s="2">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1166,28 +1150,28 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D18">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E18">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G18" s="1">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I18" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1198,19 +1182,19 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D19">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E19">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1222,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1233,31 +1217,31 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="D20">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E20">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G20" s="1">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I20" s="2">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1268,19 +1252,19 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D21">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E21">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1292,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1303,28 +1287,22 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="D22">
-        <v>41</v>
+        <v>120</v>
       </c>
       <c r="E22">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G22" s="1">
-        <v>90.23999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="H22" s="1">
-        <v>9.76</v>
+        <v>10.8</v>
       </c>
       <c r="I22" s="2">
         <v>7.8</v>
@@ -1338,66 +1316,66 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D23">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E23">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F23">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>73.53</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
-        <v>26.47</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D24">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E24">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>6.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -1408,28 +1386,28 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D25">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>71.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>28.57</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
         <v>7.1</v>
@@ -1443,31 +1421,25 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="D26">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="E26">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="F26">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>47.62</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>52.38</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>5.9</v>
+        <v>7.5</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1478,31 +1450,31 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D27">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E27">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F27">
         <v>4</v>
       </c>
       <c r="G27" s="1">
-        <v>78.95</v>
+        <v>90.2</v>
       </c>
       <c r="H27" s="1">
-        <v>21.05</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I27" s="2">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -1513,66 +1485,66 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D28">
         <v>34</v>
       </c>
       <c r="E28">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G28" s="1">
-        <v>88.23999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="H28" s="1">
-        <v>11.76</v>
+        <v>26.5</v>
       </c>
       <c r="I28" s="2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D29">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E29">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G29" s="1">
-        <v>86.05</v>
+        <v>68</v>
       </c>
       <c r="H29" s="1">
-        <v>13.95</v>
+        <v>32</v>
       </c>
       <c r="I29" s="2">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1583,31 +1555,31 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D30">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E30">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" s="1">
-        <v>87.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H30" s="1">
-        <v>12.5</v>
+        <v>28.6</v>
       </c>
       <c r="I30" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -1618,66 +1590,60 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B31" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="D31">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="E31">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="F31">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G31" s="1">
-        <v>78.05</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H31" s="1">
-        <v>21.95</v>
+        <v>21.9</v>
       </c>
       <c r="I31" s="2">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" s="1">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="D32">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E32">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G32" s="1">
-        <v>100</v>
+        <v>47.6</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <v>52.4</v>
       </c>
       <c r="I32" s="2">
-        <v>9.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -1688,31 +1654,31 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="D33">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E33">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F33">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G33" s="1">
-        <v>75</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H33" s="1">
-        <v>25</v>
+        <v>21.1</v>
       </c>
       <c r="I33" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -1723,31 +1689,25 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D34">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E34">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F34">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G34" s="1">
-        <v>76.67</v>
+        <v>62.5</v>
       </c>
       <c r="H34" s="1">
-        <v>23.33</v>
+        <v>37.5</v>
       </c>
       <c r="I34" s="2">
-        <v>7.6</v>
+        <v>6.3</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -1758,31 +1718,31 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" t="s">
         <v>51</v>
-      </c>
-      <c r="C35" t="s">
-        <v>56</v>
       </c>
       <c r="D35">
         <v>34</v>
       </c>
       <c r="E35">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G35" s="1">
-        <v>91.18000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="H35" s="1">
-        <v>8.82</v>
+        <v>11.8</v>
       </c>
       <c r="I35" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -1793,31 +1753,31 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D36">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="E36">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G36" s="1">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H36" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I36" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -1828,31 +1788,31 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D37">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E37">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G37" s="1">
-        <v>71.43000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="H37" s="1">
-        <v>28.57</v>
+        <v>12.5</v>
       </c>
       <c r="I37" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -1863,31 +1823,31 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D38">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E38">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F38">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G38" s="1">
-        <v>36.67</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H38" s="1">
-        <v>63.33</v>
+        <v>21.4</v>
       </c>
       <c r="I38" s="2">
-        <v>5</v>
+        <v>6.9</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -1898,31 +1858,25 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="D39">
-        <v>33</v>
+        <v>159</v>
       </c>
       <c r="E39">
-        <v>22</v>
+        <v>135</v>
       </c>
       <c r="F39">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G39" s="1">
-        <v>66.67</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H39" s="1">
-        <v>33.33</v>
+        <v>15.1</v>
       </c>
       <c r="I39" s="2">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -1933,36 +1887,432 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40">
+        <v>17</v>
+      </c>
+      <c r="E40">
+        <v>17</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>100</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41">
+        <v>17</v>
+      </c>
+      <c r="E41">
+        <v>17</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>100</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42">
+        <v>1173</v>
+      </c>
+      <c r="E42">
+        <v>898</v>
+      </c>
+      <c r="F42">
+        <v>275</v>
+      </c>
+      <c r="G42" s="1">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="H42" s="1">
+        <v>23.4</v>
+      </c>
+      <c r="I42" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="J42">
+        <v>2</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
         <v>21</v>
       </c>
-      <c r="B40" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43">
+        <v>32</v>
+      </c>
+      <c r="E43">
+        <v>24</v>
+      </c>
+      <c r="F43">
+        <v>8</v>
+      </c>
+      <c r="G43" s="1">
+        <v>75</v>
+      </c>
+      <c r="H43" s="1">
+        <v>25</v>
+      </c>
+      <c r="I43" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44">
+        <v>30</v>
+      </c>
+      <c r="E44">
+        <v>23</v>
+      </c>
+      <c r="F44">
+        <v>7</v>
+      </c>
+      <c r="G44" s="1">
+        <v>76.7</v>
+      </c>
+      <c r="H44" s="1">
+        <v>23.3</v>
+      </c>
+      <c r="I44" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" t="s">
+        <v>21</v>
+      </c>
+      <c r="B45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" t="s">
+        <v>56</v>
+      </c>
+      <c r="D45">
+        <v>34</v>
+      </c>
+      <c r="E45">
+        <v>31</v>
+      </c>
+      <c r="F45">
+        <v>3</v>
+      </c>
+      <c r="G45" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="H45" s="1">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I45" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" t="s">
+        <v>45</v>
+      </c>
+      <c r="D46">
+        <v>20</v>
+      </c>
+      <c r="E46">
+        <v>18</v>
+      </c>
+      <c r="F46">
+        <v>2</v>
+      </c>
+      <c r="G46" s="1">
+        <v>90</v>
+      </c>
+      <c r="H46" s="1">
+        <v>10</v>
+      </c>
+      <c r="I46" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" t="s">
+        <v>21</v>
+      </c>
+      <c r="B47" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" t="s">
+        <v>46</v>
+      </c>
+      <c r="D47">
+        <v>28</v>
+      </c>
+      <c r="E47">
+        <v>20</v>
+      </c>
+      <c r="F47">
+        <v>8</v>
+      </c>
+      <c r="G47" s="1">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="H47" s="1">
+        <v>28.6</v>
+      </c>
+      <c r="I47" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48">
+        <v>144</v>
+      </c>
+      <c r="E48">
+        <v>116</v>
+      </c>
+      <c r="F48">
+        <v>28</v>
+      </c>
+      <c r="G48" s="1">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="H48" s="1">
+        <v>19.4</v>
+      </c>
+      <c r="I48" s="2">
+        <v>7.1</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" t="s">
         <v>57</v>
       </c>
-      <c r="D40">
+      <c r="D49">
+        <v>30</v>
+      </c>
+      <c r="E49">
+        <v>11</v>
+      </c>
+      <c r="F49">
+        <v>19</v>
+      </c>
+      <c r="G49" s="1">
+        <v>36.7</v>
+      </c>
+      <c r="H49" s="1">
+        <v>63.3</v>
+      </c>
+      <c r="I49" s="2">
+        <v>5</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" t="s">
+        <v>58</v>
+      </c>
+      <c r="D50">
         <v>33</v>
       </c>
-      <c r="E40">
+      <c r="E50">
+        <v>22</v>
+      </c>
+      <c r="F50">
+        <v>11</v>
+      </c>
+      <c r="G50" s="1">
+        <v>66.7</v>
+      </c>
+      <c r="H50" s="1">
+        <v>33.3</v>
+      </c>
+      <c r="I50" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
+        <v>22</v>
+      </c>
+      <c r="B51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" t="s">
+        <v>59</v>
+      </c>
+      <c r="D51">
+        <v>33</v>
+      </c>
+      <c r="E51">
         <v>18</v>
       </c>
-      <c r="F40">
+      <c r="F51">
         <v>15</v>
       </c>
-      <c r="G40" s="1">
-        <v>54.55</v>
-      </c>
-      <c r="H40" s="1">
-        <v>45.45</v>
-      </c>
-      <c r="I40" s="2">
+      <c r="G51" s="1">
+        <v>54.5</v>
+      </c>
+      <c r="H51" s="1">
+        <v>45.5</v>
+      </c>
+      <c r="I51" s="2">
         <v>5.8</v>
       </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40" s="1">
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52">
+        <v>96</v>
+      </c>
+      <c r="E52">
+        <v>51</v>
+      </c>
+      <c r="F52">
+        <v>45</v>
+      </c>
+      <c r="G52" s="1">
+        <v>53.1</v>
+      </c>
+      <c r="H52" s="1">
+        <v>46.9</v>
+      </c>
+      <c r="I52" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1973,11 +2323,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -2023,31 +2373,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="D2">
         <v>27</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>33.3</v>
+      </c>
+      <c r="I2" s="2">
+        <v>6.7</v>
       </c>
       <c r="J2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2058,28 +2411,31 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>60</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.1</v>
       </c>
       <c r="J3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2090,28 +2446,31 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>26</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>88.5</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>11.5</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.6</v>
       </c>
       <c r="J4">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2119,31 +2478,34 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="D5">
         <v>17</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>11.8</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7.1</v>
       </c>
       <c r="J5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2151,63 +2513,63 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D6">
         <v>19</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>10.5</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.3</v>
       </c>
       <c r="J6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>28.6</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2215,31 +2577,34 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>62.2</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>37.8</v>
+      </c>
+      <c r="I8" s="2">
+        <v>6.2</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2247,31 +2612,34 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D9">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F9">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>48.4</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>51.6</v>
+      </c>
+      <c r="I9" s="2">
+        <v>5.8</v>
       </c>
       <c r="J9">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2279,31 +2647,34 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="D10">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>58.5</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>41.5</v>
+      </c>
+      <c r="I10" s="2">
+        <v>6.2</v>
       </c>
       <c r="J10">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2311,31 +2682,34 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11">
         <v>31</v>
       </c>
-      <c r="C11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11">
-        <v>38</v>
-      </c>
       <c r="E11">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>74.2</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>25.8</v>
+      </c>
+      <c r="I11" s="2">
+        <v>6.1</v>
       </c>
       <c r="J11">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2343,31 +2717,34 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D12">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F12">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>7.9</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.3</v>
       </c>
       <c r="J12">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2375,159 +2752,162 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="D13">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F13">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>64.3</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>35.7</v>
+      </c>
+      <c r="I13" s="2">
+        <v>5.9</v>
       </c>
       <c r="J13">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14">
+        <v>41</v>
+      </c>
+      <c r="E14">
+        <v>28</v>
+      </c>
+      <c r="F14">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14">
-        <v>39</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>39</v>
-      </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>68.3</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>31.7</v>
+      </c>
+      <c r="I14" s="2">
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="D15">
-        <v>36</v>
+        <v>247</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="F15">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>67.2</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>32.8</v>
+      </c>
+      <c r="I15" s="2">
+        <v>6.2</v>
       </c>
       <c r="J15">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D16">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F16">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>25.6</v>
+      </c>
+      <c r="I16" s="2">
+        <v>6.5</v>
       </c>
       <c r="J16">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D17">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F17">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>25.6</v>
+      </c>
+      <c r="I17" s="2">
+        <v>6.5</v>
       </c>
       <c r="J17">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2535,2151 +2915,1169 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D18">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F18">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>16.7</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D19">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F19">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>8.5</v>
       </c>
       <c r="J19">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="D20">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>33.3</v>
+      </c>
+      <c r="I20" s="2">
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D21">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F21">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>7.8</v>
       </c>
       <c r="J21">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="D22">
-        <v>41</v>
+        <v>120</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="F22">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>89.2</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>10.8</v>
+      </c>
+      <c r="I22" s="2">
+        <v>7.8</v>
       </c>
       <c r="J22">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D23">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F23">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>7.3</v>
       </c>
       <c r="J23">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D24">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F24">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J24">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D25">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <v>7.1</v>
       </c>
       <c r="J25">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="D26">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F26">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>7.5</v>
       </c>
       <c r="J26">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D27">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F27">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I27" s="2">
+        <v>7.8</v>
       </c>
       <c r="J27">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D28">
         <v>34</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F28">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>73.5</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>26.5</v>
+      </c>
+      <c r="I28" s="2">
+        <v>6.8</v>
       </c>
       <c r="J28">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D29">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F29">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>32</v>
+      </c>
+      <c r="I29" s="2">
+        <v>6.6</v>
       </c>
       <c r="J29">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D30">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>28.6</v>
+      </c>
+      <c r="I30" s="2">
+        <v>7.1</v>
       </c>
       <c r="J30">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B31" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="D31">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="F31">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>21.9</v>
+      </c>
+      <c r="I31" s="2">
+        <v>7.1</v>
       </c>
       <c r="J31">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="D32">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F32">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>47.6</v>
       </c>
       <c r="H32" s="1">
-        <v>100</v>
+        <v>52.4</v>
+      </c>
+      <c r="I32" s="2">
+        <v>5.9</v>
       </c>
       <c r="J32">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="D33">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F33">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>21.1</v>
+      </c>
+      <c r="I33" s="2">
+        <v>6.7</v>
       </c>
       <c r="J33">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="D34">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F34">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="H34" s="1">
-        <v>100</v>
+        <v>37.5</v>
+      </c>
+      <c r="I34" s="2">
+        <v>6.3</v>
       </c>
       <c r="J34">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" t="s">
         <v>51</v>
-      </c>
-      <c r="C35" t="s">
-        <v>56</v>
       </c>
       <c r="D35">
         <v>34</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F35">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="H35" s="1">
-        <v>100</v>
+        <v>11.8</v>
+      </c>
+      <c r="I35" s="2">
+        <v>7.3</v>
       </c>
       <c r="J35">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D36">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F36">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H36" s="1">
-        <v>100</v>
+        <v>14</v>
+      </c>
+      <c r="I36" s="2">
+        <v>7.3</v>
       </c>
       <c r="J36">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D37">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F37">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H37" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I37" s="2">
+        <v>7</v>
       </c>
       <c r="J37">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D38">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F38">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H38" s="1">
-        <v>100</v>
+        <v>21.4</v>
+      </c>
+      <c r="I38" s="2">
+        <v>6.9</v>
       </c>
       <c r="J38">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="D39">
-        <v>33</v>
+        <v>159</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="F39">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H39" s="1">
-        <v>100</v>
+        <v>15.1</v>
+      </c>
+      <c r="I39" s="2">
+        <v>7.1</v>
       </c>
       <c r="J39">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40">
+        <v>17</v>
+      </c>
+      <c r="E40">
+        <v>17</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>100</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41">
+        <v>17</v>
+      </c>
+      <c r="E41">
+        <v>17</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>100</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42">
+        <v>1173</v>
+      </c>
+      <c r="E42">
+        <v>898</v>
+      </c>
+      <c r="F42">
+        <v>275</v>
+      </c>
+      <c r="G42" s="1">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="H42" s="1">
+        <v>23.4</v>
+      </c>
+      <c r="I42" s="2">
+        <v>7</v>
+      </c>
+      <c r="J42">
+        <v>2</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
         <v>21</v>
       </c>
-      <c r="B40" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43">
+        <v>32</v>
+      </c>
+      <c r="E43">
+        <v>24</v>
+      </c>
+      <c r="F43">
+        <v>8</v>
+      </c>
+      <c r="G43" s="1">
+        <v>75</v>
+      </c>
+      <c r="H43" s="1">
+        <v>25</v>
+      </c>
+      <c r="I43" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44">
+        <v>30</v>
+      </c>
+      <c r="E44">
+        <v>23</v>
+      </c>
+      <c r="F44">
+        <v>7</v>
+      </c>
+      <c r="G44" s="1">
+        <v>76.7</v>
+      </c>
+      <c r="H44" s="1">
+        <v>23.3</v>
+      </c>
+      <c r="I44" s="2">
+        <v>7.7</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" t="s">
+        <v>21</v>
+      </c>
+      <c r="B45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" t="s">
+        <v>56</v>
+      </c>
+      <c r="D45">
+        <v>34</v>
+      </c>
+      <c r="E45">
+        <v>31</v>
+      </c>
+      <c r="F45">
+        <v>3</v>
+      </c>
+      <c r="G45" s="1">
+        <v>91.2</v>
+      </c>
+      <c r="H45" s="1">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I45" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" t="s">
+        <v>45</v>
+      </c>
+      <c r="D46">
+        <v>20</v>
+      </c>
+      <c r="E46">
+        <v>18</v>
+      </c>
+      <c r="F46">
+        <v>2</v>
+      </c>
+      <c r="G46" s="1">
+        <v>90</v>
+      </c>
+      <c r="H46" s="1">
+        <v>10</v>
+      </c>
+      <c r="I46" s="2">
+        <v>7.3</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" t="s">
+        <v>21</v>
+      </c>
+      <c r="B47" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" t="s">
+        <v>46</v>
+      </c>
+      <c r="D47">
+        <v>28</v>
+      </c>
+      <c r="E47">
+        <v>20</v>
+      </c>
+      <c r="F47">
+        <v>8</v>
+      </c>
+      <c r="G47" s="1">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="H47" s="1">
+        <v>28.6</v>
+      </c>
+      <c r="I47" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48">
+        <v>144</v>
+      </c>
+      <c r="E48">
+        <v>116</v>
+      </c>
+      <c r="F48">
+        <v>28</v>
+      </c>
+      <c r="G48" s="1">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="H48" s="1">
+        <v>19.4</v>
+      </c>
+      <c r="I48" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" t="s">
         <v>57</v>
       </c>
-      <c r="D40">
+      <c r="D49">
+        <v>30</v>
+      </c>
+      <c r="E49">
+        <v>11</v>
+      </c>
+      <c r="F49">
+        <v>19</v>
+      </c>
+      <c r="G49" s="1">
+        <v>36.7</v>
+      </c>
+      <c r="H49" s="1">
+        <v>63.3</v>
+      </c>
+      <c r="I49" s="2">
+        <v>5.6</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" t="s">
+        <v>58</v>
+      </c>
+      <c r="D50">
         <v>33</v>
       </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40">
+      <c r="E50">
+        <v>22</v>
+      </c>
+      <c r="F50">
+        <v>11</v>
+      </c>
+      <c r="G50" s="1">
+        <v>66.7</v>
+      </c>
+      <c r="H50" s="1">
+        <v>33.3</v>
+      </c>
+      <c r="I50" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
+        <v>22</v>
+      </c>
+      <c r="B51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" t="s">
+        <v>59</v>
+      </c>
+      <c r="D51">
         <v>33</v>
       </c>
-      <c r="G40" s="1">
-        <v>0</v>
-      </c>
-      <c r="H40" s="1">
-        <v>100</v>
-      </c>
-      <c r="J40">
-        <v>33</v>
-      </c>
-      <c r="K40" s="1">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K40"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="1"/>
-    <col min="9" max="9" width="9.140625" style="2"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="E51">
+        <v>18</v>
+      </c>
+      <c r="F51">
+        <v>15</v>
+      </c>
+      <c r="G51" s="1">
+        <v>54.5</v>
+      </c>
+      <c r="H51" s="1">
+        <v>45.5</v>
+      </c>
+      <c r="I51" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2">
-        <v>27</v>
-      </c>
-      <c r="E2">
-        <v>18</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1">
-        <v>66.67</v>
-      </c>
-      <c r="H2" s="1">
-        <v>33.33</v>
-      </c>
-      <c r="I2" s="2">
-        <v>6.7</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3">
-        <v>30</v>
-      </c>
-      <c r="E3">
-        <v>12</v>
-      </c>
-      <c r="F3">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1">
-        <v>40</v>
-      </c>
-      <c r="H3" s="1">
-        <v>60</v>
-      </c>
-      <c r="I3" s="2">
-        <v>6.1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4">
-        <v>26</v>
-      </c>
-      <c r="E4">
-        <v>23</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4" s="1">
-        <v>88.45999999999999</v>
-      </c>
-      <c r="H4" s="1">
-        <v>11.54</v>
-      </c>
-      <c r="I4" s="2">
-        <v>7.6</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5">
-        <v>17</v>
-      </c>
-      <c r="E5">
-        <v>15</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5" s="1">
-        <v>88.23999999999999</v>
-      </c>
-      <c r="H5" s="1">
-        <v>11.76</v>
-      </c>
-      <c r="I5" s="2">
-        <v>7.1</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6">
-        <v>19</v>
-      </c>
-      <c r="E6">
-        <v>17</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6" s="1">
-        <v>89.47</v>
-      </c>
-      <c r="H6" s="1">
-        <v>10.53</v>
-      </c>
-      <c r="I6" s="2">
-        <v>7.3</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7">
-        <v>37</v>
-      </c>
-      <c r="E7">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>14</v>
-      </c>
-      <c r="G7" s="1">
-        <v>62.16</v>
-      </c>
-      <c r="H7" s="1">
-        <v>37.84</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="D52">
+        <v>96</v>
+      </c>
+      <c r="E52">
+        <v>51</v>
+      </c>
+      <c r="F52">
+        <v>45</v>
+      </c>
+      <c r="G52" s="1">
+        <v>53.1</v>
+      </c>
+      <c r="H52" s="1">
+        <v>46.9</v>
+      </c>
+      <c r="I52" s="2">
         <v>6.2</v>
       </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8">
-        <v>31</v>
-      </c>
-      <c r="E8">
-        <v>15</v>
-      </c>
-      <c r="F8">
-        <v>16</v>
-      </c>
-      <c r="G8" s="1">
-        <v>48.39</v>
-      </c>
-      <c r="H8" s="1">
-        <v>51.61</v>
-      </c>
-      <c r="I8" s="2">
-        <v>5.8</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9">
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <v>25</v>
-      </c>
-      <c r="F9">
-        <v>17</v>
-      </c>
-      <c r="G9" s="1">
-        <v>59.52</v>
-      </c>
-      <c r="H9" s="1">
-        <v>40.48</v>
-      </c>
-      <c r="I9" s="2">
-        <v>6.3</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10">
-        <v>31</v>
-      </c>
-      <c r="E10">
-        <v>23</v>
-      </c>
-      <c r="F10">
-        <v>8</v>
-      </c>
-      <c r="G10" s="1">
-        <v>74.19</v>
-      </c>
-      <c r="H10" s="1">
-        <v>25.81</v>
-      </c>
-      <c r="I10" s="2">
-        <v>6.1</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11">
-        <v>38</v>
-      </c>
-      <c r="E11">
-        <v>35</v>
-      </c>
-      <c r="F11">
-        <v>3</v>
-      </c>
-      <c r="G11" s="1">
-        <v>92.11</v>
-      </c>
-      <c r="H11" s="1">
-        <v>7.89</v>
-      </c>
-      <c r="I11" s="2">
-        <v>7.3</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12">
-        <v>28</v>
-      </c>
-      <c r="E12">
-        <v>18</v>
-      </c>
-      <c r="F12">
-        <v>10</v>
-      </c>
-      <c r="G12" s="1">
-        <v>64.29000000000001</v>
-      </c>
-      <c r="H12" s="1">
-        <v>35.71</v>
-      </c>
-      <c r="I12" s="2">
-        <v>5.9</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13">
-        <v>41</v>
-      </c>
-      <c r="E13">
-        <v>28</v>
-      </c>
-      <c r="F13">
-        <v>13</v>
-      </c>
-      <c r="G13" s="1">
-        <v>68.29000000000001</v>
-      </c>
-      <c r="H13" s="1">
-        <v>31.71</v>
-      </c>
-      <c r="I13" s="2">
-        <v>6</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14">
-        <v>39</v>
-      </c>
-      <c r="E14">
-        <v>29</v>
-      </c>
-      <c r="F14">
-        <v>10</v>
-      </c>
-      <c r="G14" s="1">
-        <v>74.36</v>
-      </c>
-      <c r="H14" s="1">
-        <v>25.64</v>
-      </c>
-      <c r="I14" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15">
-        <v>36</v>
-      </c>
-      <c r="E15">
-        <v>30</v>
-      </c>
-      <c r="F15">
-        <v>6</v>
-      </c>
-      <c r="G15" s="1">
-        <v>83.33</v>
-      </c>
-      <c r="H15" s="1">
-        <v>16.67</v>
-      </c>
-      <c r="I15" s="2">
-        <v>8</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16">
-        <v>32</v>
-      </c>
-      <c r="E16">
-        <v>32</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1">
-        <v>100</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
-        <v>8.5</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17">
-        <v>21</v>
-      </c>
-      <c r="E17">
-        <v>14</v>
-      </c>
-      <c r="F17">
-        <v>7</v>
-      </c>
-      <c r="G17" s="1">
-        <v>66.67</v>
-      </c>
-      <c r="H17" s="1">
-        <v>33.33</v>
-      </c>
-      <c r="I17" s="2">
-        <v>7</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18">
-        <v>31</v>
-      </c>
-      <c r="E18">
-        <v>31</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1">
-        <v>100</v>
-      </c>
-      <c r="H18" s="1">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2">
-        <v>7.8</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19">
-        <v>30</v>
-      </c>
-      <c r="E19">
-        <v>30</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19" s="1">
-        <v>100</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2">
-        <v>7.3</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20">
-        <v>20</v>
-      </c>
-      <c r="E20">
-        <v>20</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1">
-        <v>100</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21">
-        <v>28</v>
-      </c>
-      <c r="E21">
-        <v>28</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
-        <v>100</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2">
-        <v>7.1</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22">
-        <v>41</v>
-      </c>
-      <c r="E22">
-        <v>37</v>
-      </c>
-      <c r="F22">
-        <v>4</v>
-      </c>
-      <c r="G22" s="1">
-        <v>90.23999999999999</v>
-      </c>
-      <c r="H22" s="1">
-        <v>9.76</v>
-      </c>
-      <c r="I22" s="2">
-        <v>7.8</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23">
-        <v>34</v>
-      </c>
-      <c r="E23">
-        <v>25</v>
-      </c>
-      <c r="F23">
-        <v>9</v>
-      </c>
-      <c r="G23" s="1">
-        <v>73.53</v>
-      </c>
-      <c r="H23" s="1">
-        <v>26.47</v>
-      </c>
-      <c r="I23" s="2">
-        <v>6.8</v>
-      </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-      <c r="K23" s="1">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24">
-        <v>25</v>
-      </c>
-      <c r="E24">
-        <v>17</v>
-      </c>
-      <c r="F24">
-        <v>8</v>
-      </c>
-      <c r="G24" s="1">
-        <v>68</v>
-      </c>
-      <c r="H24" s="1">
-        <v>32</v>
-      </c>
-      <c r="I24" s="2">
-        <v>6.6</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25">
-        <v>14</v>
-      </c>
-      <c r="E25">
-        <v>10</v>
-      </c>
-      <c r="F25">
-        <v>4</v>
-      </c>
-      <c r="G25" s="1">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="H25" s="1">
-        <v>28.57</v>
-      </c>
-      <c r="I25" s="2">
-        <v>7.1</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26">
-        <v>21</v>
-      </c>
-      <c r="E26">
-        <v>10</v>
-      </c>
-      <c r="F26">
-        <v>11</v>
-      </c>
-      <c r="G26" s="1">
-        <v>47.62</v>
-      </c>
-      <c r="H26" s="1">
-        <v>52.38</v>
-      </c>
-      <c r="I26" s="2">
-        <v>5.9</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27">
-        <v>19</v>
-      </c>
-      <c r="E27">
-        <v>15</v>
-      </c>
-      <c r="F27">
-        <v>4</v>
-      </c>
-      <c r="G27" s="1">
-        <v>78.95</v>
-      </c>
-      <c r="H27" s="1">
-        <v>21.05</v>
-      </c>
-      <c r="I27" s="2">
-        <v>6.7</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28">
-        <v>34</v>
-      </c>
-      <c r="E28">
-        <v>30</v>
-      </c>
-      <c r="F28">
-        <v>4</v>
-      </c>
-      <c r="G28" s="1">
-        <v>88.23999999999999</v>
-      </c>
-      <c r="H28" s="1">
-        <v>11.76</v>
-      </c>
-      <c r="I28" s="2">
-        <v>7.3</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" t="s">
-        <v>18</v>
-      </c>
-      <c r="B29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29">
-        <v>43</v>
-      </c>
-      <c r="E29">
-        <v>37</v>
-      </c>
-      <c r="F29">
-        <v>6</v>
-      </c>
-      <c r="G29" s="1">
-        <v>86.05</v>
-      </c>
-      <c r="H29" s="1">
-        <v>13.95</v>
-      </c>
-      <c r="I29" s="2">
-        <v>7.3</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" t="s">
-        <v>18</v>
-      </c>
-      <c r="B30" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" t="s">
-        <v>57</v>
-      </c>
-      <c r="D30">
-        <v>40</v>
-      </c>
-      <c r="E30">
-        <v>35</v>
-      </c>
-      <c r="F30">
-        <v>5</v>
-      </c>
-      <c r="G30" s="1">
-        <v>87.5</v>
-      </c>
-      <c r="H30" s="1">
-        <v>12.5</v>
-      </c>
-      <c r="I30" s="2">
-        <v>7</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B31" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31">
-        <v>41</v>
-      </c>
-      <c r="E31">
-        <v>32</v>
-      </c>
-      <c r="F31">
-        <v>9</v>
-      </c>
-      <c r="G31" s="1">
-        <v>78.05</v>
-      </c>
-      <c r="H31" s="1">
-        <v>21.95</v>
-      </c>
-      <c r="I31" s="2">
-        <v>6.8</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32" t="s">
-        <v>58</v>
-      </c>
-      <c r="D32">
-        <v>17</v>
-      </c>
-      <c r="E32">
-        <v>17</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32" s="1">
-        <v>100</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" t="s">
-        <v>20</v>
-      </c>
-      <c r="B33" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33">
-        <v>32</v>
-      </c>
-      <c r="E33">
-        <v>24</v>
-      </c>
-      <c r="F33">
-        <v>8</v>
-      </c>
-      <c r="G33" s="1">
-        <v>75</v>
-      </c>
-      <c r="H33" s="1">
-        <v>25</v>
-      </c>
-      <c r="I33" s="2">
-        <v>6.7</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" t="s">
-        <v>56</v>
-      </c>
-      <c r="D34">
-        <v>30</v>
-      </c>
-      <c r="E34">
-        <v>23</v>
-      </c>
-      <c r="F34">
-        <v>7</v>
-      </c>
-      <c r="G34" s="1">
-        <v>76.67</v>
-      </c>
-      <c r="H34" s="1">
-        <v>23.33</v>
-      </c>
-      <c r="I34" s="2">
-        <v>7.7</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" t="s">
-        <v>20</v>
-      </c>
-      <c r="B35" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" t="s">
-        <v>56</v>
-      </c>
-      <c r="D35">
-        <v>34</v>
-      </c>
-      <c r="E35">
-        <v>31</v>
-      </c>
-      <c r="F35">
-        <v>3</v>
-      </c>
-      <c r="G35" s="1">
-        <v>91.18000000000001</v>
-      </c>
-      <c r="H35" s="1">
-        <v>8.82</v>
-      </c>
-      <c r="I35" s="2">
-        <v>7.6</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" t="s">
-        <v>20</v>
-      </c>
-      <c r="B36" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" t="s">
-        <v>56</v>
-      </c>
-      <c r="D36">
-        <v>20</v>
-      </c>
-      <c r="E36">
-        <v>18</v>
-      </c>
-      <c r="F36">
-        <v>2</v>
-      </c>
-      <c r="G36" s="1">
-        <v>90</v>
-      </c>
-      <c r="H36" s="1">
-        <v>10</v>
-      </c>
-      <c r="I36" s="2">
-        <v>7.3</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" t="s">
-        <v>20</v>
-      </c>
-      <c r="B37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" t="s">
-        <v>56</v>
-      </c>
-      <c r="D37">
-        <v>28</v>
-      </c>
-      <c r="E37">
-        <v>20</v>
-      </c>
-      <c r="F37">
-        <v>8</v>
-      </c>
-      <c r="G37" s="1">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="H37" s="1">
-        <v>28.57</v>
-      </c>
-      <c r="I37" s="2">
-        <v>6.8</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
-      <c r="A38" t="s">
-        <v>21</v>
-      </c>
-      <c r="B38" t="s">
-        <v>52</v>
-      </c>
-      <c r="C38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D38">
-        <v>30</v>
-      </c>
-      <c r="E38">
-        <v>11</v>
-      </c>
-      <c r="F38">
-        <v>19</v>
-      </c>
-      <c r="G38" s="1">
-        <v>36.67</v>
-      </c>
-      <c r="H38" s="1">
-        <v>63.33</v>
-      </c>
-      <c r="I38" s="2">
-        <v>5.6</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" t="s">
-        <v>57</v>
-      </c>
-      <c r="D39">
-        <v>33</v>
-      </c>
-      <c r="E39">
-        <v>22</v>
-      </c>
-      <c r="F39">
-        <v>11</v>
-      </c>
-      <c r="G39" s="1">
-        <v>66.67</v>
-      </c>
-      <c r="H39" s="1">
-        <v>33.33</v>
-      </c>
-      <c r="I39" s="2">
-        <v>6.9</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
-      <c r="A40" t="s">
-        <v>21</v>
-      </c>
-      <c r="B40" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" t="s">
-        <v>57</v>
-      </c>
-      <c r="D40">
-        <v>33</v>
-      </c>
-      <c r="E40">
-        <v>18</v>
-      </c>
-      <c r="F40">
-        <v>15</v>
-      </c>
-      <c r="G40" s="1">
-        <v>54.55</v>
-      </c>
-      <c r="H40" s="1">
-        <v>45.45</v>
-      </c>
-      <c r="I40" s="2">
-        <v>6.1</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40" s="1">
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="61">
   <si>
     <t>Docente</t>
   </si>
@@ -77,9 +77,6 @@
     <t>Santiago Hernández Mariana</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
@@ -92,10 +89,16 @@
     <t>PROBABILIDAD Y ESTADÍSTICA</t>
   </si>
   <si>
+    <t>Totales Docente</t>
+  </si>
+  <si>
     <t>GEOMETRÍA Y TRIGONOMETRÍA</t>
   </si>
   <si>
     <t>MATEMÁTICAS APLICADAS</t>
+  </si>
+  <si>
+    <t>Totales Generales</t>
   </si>
   <si>
     <t>4APM</t>
@@ -562,7 +565,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -608,10 +611,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>27</v>
@@ -643,10 +646,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3">
         <v>30</v>
@@ -678,10 +681,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>26</v>
@@ -713,10 +716,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>17</v>
@@ -748,10 +751,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6">
         <v>19</v>
@@ -782,6 +785,9 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
       <c r="D7">
         <v>119</v>
       </c>
@@ -815,7 +821,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>37</v>
@@ -850,7 +856,7 @@
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9">
         <v>31</v>
@@ -885,7 +891,7 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10">
         <v>41</v>
@@ -917,10 +923,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11">
         <v>31</v>
@@ -952,10 +958,10 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D12">
         <v>38</v>
@@ -987,10 +993,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13">
         <v>28</v>
@@ -1022,10 +1028,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14">
         <v>41</v>
@@ -1056,6 +1062,9 @@
       <c r="A15" t="s">
         <v>12</v>
       </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
       <c r="D15">
         <v>247</v>
       </c>
@@ -1089,7 +1098,7 @@
         <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16">
         <v>39</v>
@@ -1120,6 +1129,9 @@
       <c r="A17" t="s">
         <v>13</v>
       </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
       <c r="D17">
         <v>39</v>
       </c>
@@ -1150,10 +1162,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D18">
         <v>36</v>
@@ -1185,10 +1197,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D19">
         <v>32</v>
@@ -1220,10 +1232,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D20">
         <v>21</v>
@@ -1255,10 +1267,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D21">
         <v>31</v>
@@ -1289,6 +1301,9 @@
       <c r="A22" t="s">
         <v>14</v>
       </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
       <c r="D22">
         <v>120</v>
       </c>
@@ -1322,7 +1337,7 @@
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D23">
         <v>30</v>
@@ -1357,7 +1372,7 @@
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D24">
         <v>20</v>
@@ -1392,7 +1407,7 @@
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D25">
         <v>28</v>
@@ -1423,6 +1438,9 @@
       <c r="A26" t="s">
         <v>15</v>
       </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
       <c r="D26">
         <v>78</v>
       </c>
@@ -1453,10 +1471,10 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D27">
         <v>41</v>
@@ -1488,10 +1506,10 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D28">
         <v>34</v>
@@ -1523,10 +1541,10 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D29">
         <v>25</v>
@@ -1558,10 +1576,10 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D30">
         <v>14</v>
@@ -1592,6 +1610,9 @@
       <c r="A31" t="s">
         <v>16</v>
       </c>
+      <c r="B31" t="s">
+        <v>24</v>
+      </c>
       <c r="D31">
         <v>114</v>
       </c>
@@ -1625,7 +1646,7 @@
         <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D32">
         <v>21</v>
@@ -1660,7 +1681,7 @@
         <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D33">
         <v>19</v>
@@ -1691,6 +1712,9 @@
       <c r="A34" t="s">
         <v>17</v>
       </c>
+      <c r="B34" t="s">
+        <v>24</v>
+      </c>
       <c r="D34">
         <v>40</v>
       </c>
@@ -1724,7 +1748,7 @@
         <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1759,7 +1783,7 @@
         <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D36">
         <v>43</v>
@@ -1794,7 +1818,7 @@
         <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D37">
         <v>40</v>
@@ -1829,7 +1853,7 @@
         <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D38">
         <v>42</v>
@@ -1860,6 +1884,9 @@
       <c r="A39" t="s">
         <v>18</v>
       </c>
+      <c r="B39" t="s">
+        <v>24</v>
+      </c>
       <c r="D39">
         <v>159</v>
       </c>
@@ -1893,7 +1920,7 @@
         <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D40">
         <v>17</v>
@@ -1924,6 +1951,9 @@
       <c r="A41" t="s">
         <v>19</v>
       </c>
+      <c r="B41" t="s">
+        <v>24</v>
+      </c>
       <c r="D41">
         <v>17</v>
       </c>
@@ -1953,58 +1983,64 @@
       <c r="A42" t="s">
         <v>20</v>
       </c>
+      <c r="B42" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
+        <v>56</v>
+      </c>
       <c r="D42">
-        <v>1173</v>
+        <v>32</v>
       </c>
       <c r="E42">
-        <v>898</v>
+        <v>24</v>
       </c>
       <c r="F42">
-        <v>275</v>
+        <v>8</v>
       </c>
       <c r="G42" s="1">
-        <v>76.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="H42" s="1">
-        <v>23.4</v>
+        <v>25</v>
       </c>
       <c r="I42" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="J42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B43" t="s">
         <v>23</v>
       </c>
       <c r="C43" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D43">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E43">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G43" s="1">
-        <v>75</v>
+        <v>76.7</v>
       </c>
       <c r="H43" s="1">
-        <v>25</v>
+        <v>23.3</v>
       </c>
       <c r="I43" s="2">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -2015,28 +2051,28 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D44">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E44">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F44">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G44" s="1">
-        <v>76.7</v>
+        <v>91.2</v>
       </c>
       <c r="H44" s="1">
-        <v>23.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I44" s="2">
         <v>7.6</v>
@@ -2050,31 +2086,31 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D45">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E45">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45" s="1">
-        <v>91.2</v>
+        <v>90</v>
       </c>
       <c r="H45" s="1">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I45" s="2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -2085,31 +2121,31 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C46" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D46">
+        <v>28</v>
+      </c>
+      <c r="E46">
         <v>20</v>
       </c>
-      <c r="E46">
-        <v>18</v>
-      </c>
       <c r="F46">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G46" s="1">
-        <v>90</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H46" s="1">
-        <v>10</v>
+        <v>28.6</v>
       </c>
       <c r="I46" s="2">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -2120,31 +2156,28 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
         <v>24</v>
       </c>
-      <c r="C47" t="s">
-        <v>46</v>
-      </c>
       <c r="D47">
+        <v>144</v>
+      </c>
+      <c r="E47">
+        <v>116</v>
+      </c>
+      <c r="F47">
         <v>28</v>
       </c>
-      <c r="E47">
-        <v>20</v>
-      </c>
-      <c r="F47">
-        <v>8</v>
-      </c>
       <c r="G47" s="1">
-        <v>71.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H47" s="1">
-        <v>28.6</v>
+        <v>19.4</v>
       </c>
       <c r="I47" s="2">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -2157,23 +2190,29 @@
       <c r="A48" t="s">
         <v>21</v>
       </c>
+      <c r="B48" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" t="s">
+        <v>58</v>
+      </c>
       <c r="D48">
-        <v>144</v>
+        <v>30</v>
       </c>
       <c r="E48">
-        <v>116</v>
+        <v>11</v>
       </c>
       <c r="F48">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G48" s="1">
-        <v>80.59999999999999</v>
+        <v>36.7</v>
       </c>
       <c r="H48" s="1">
-        <v>19.4</v>
+        <v>63.3</v>
       </c>
       <c r="I48" s="2">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -2184,31 +2223,31 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
         <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D49">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E49">
+        <v>22</v>
+      </c>
+      <c r="F49">
         <v>11</v>
       </c>
-      <c r="F49">
-        <v>19</v>
-      </c>
       <c r="G49" s="1">
-        <v>36.7</v>
+        <v>66.7</v>
       </c>
       <c r="H49" s="1">
-        <v>63.3</v>
+        <v>33.3</v>
       </c>
       <c r="I49" s="2">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -2219,31 +2258,31 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B50" t="s">
         <v>25</v>
       </c>
       <c r="C50" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D50">
         <v>33</v>
       </c>
       <c r="E50">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F50">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G50" s="1">
-        <v>66.7</v>
+        <v>54.5</v>
       </c>
       <c r="H50" s="1">
-        <v>33.3</v>
+        <v>45.5</v>
       </c>
       <c r="I50" s="2">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -2254,31 +2293,28 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
-      </c>
-      <c r="C51" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="D51">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="E51">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="F51">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G51" s="1">
-        <v>54.5</v>
+        <v>53.1</v>
       </c>
       <c r="H51" s="1">
-        <v>45.5</v>
+        <v>46.9</v>
       </c>
       <c r="I51" s="2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -2288,32 +2324,32 @@
       </c>
     </row>
     <row r="52" spans="1:11">
-      <c r="A52" t="s">
-        <v>22</v>
+      <c r="B52" t="s">
+        <v>27</v>
       </c>
       <c r="D52">
-        <v>96</v>
+        <v>1173</v>
       </c>
       <c r="E52">
-        <v>51</v>
+        <v>898</v>
       </c>
       <c r="F52">
-        <v>45</v>
+        <v>275</v>
       </c>
       <c r="G52" s="1">
-        <v>53.1</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="H52" s="1">
-        <v>46.9</v>
+        <v>23.4</v>
       </c>
       <c r="I52" s="2">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K52" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -2373,10 +2409,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>27</v>
@@ -2408,10 +2444,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3">
         <v>30</v>
@@ -2443,10 +2479,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>26</v>
@@ -2478,10 +2514,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>17</v>
@@ -2513,10 +2549,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6">
         <v>19</v>
@@ -2547,6 +2583,9 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
       <c r="D7">
         <v>119</v>
       </c>
@@ -2580,7 +2619,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>37</v>
@@ -2615,7 +2654,7 @@
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9">
         <v>31</v>
@@ -2650,7 +2689,7 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10">
         <v>41</v>
@@ -2682,10 +2721,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11">
         <v>31</v>
@@ -2717,10 +2756,10 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D12">
         <v>38</v>
@@ -2752,10 +2791,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13">
         <v>28</v>
@@ -2787,10 +2826,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14">
         <v>41</v>
@@ -2821,6 +2860,9 @@
       <c r="A15" t="s">
         <v>12</v>
       </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
       <c r="D15">
         <v>247</v>
       </c>
@@ -2854,7 +2896,7 @@
         <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16">
         <v>39</v>
@@ -2885,6 +2927,9 @@
       <c r="A17" t="s">
         <v>13</v>
       </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
       <c r="D17">
         <v>39</v>
       </c>
@@ -2915,10 +2960,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D18">
         <v>36</v>
@@ -2950,10 +2995,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D19">
         <v>32</v>
@@ -2985,10 +3030,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D20">
         <v>21</v>
@@ -3020,10 +3065,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D21">
         <v>31</v>
@@ -3054,6 +3099,9 @@
       <c r="A22" t="s">
         <v>14</v>
       </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
       <c r="D22">
         <v>120</v>
       </c>
@@ -3087,7 +3135,7 @@
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D23">
         <v>30</v>
@@ -3122,7 +3170,7 @@
         <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D24">
         <v>20</v>
@@ -3157,7 +3205,7 @@
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D25">
         <v>28</v>
@@ -3188,6 +3236,9 @@
       <c r="A26" t="s">
         <v>15</v>
       </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
       <c r="D26">
         <v>78</v>
       </c>
@@ -3218,10 +3269,10 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D27">
         <v>41</v>
@@ -3253,10 +3304,10 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D28">
         <v>34</v>
@@ -3288,10 +3339,10 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D29">
         <v>25</v>
@@ -3323,10 +3374,10 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D30">
         <v>14</v>
@@ -3357,6 +3408,9 @@
       <c r="A31" t="s">
         <v>16</v>
       </c>
+      <c r="B31" t="s">
+        <v>24</v>
+      </c>
       <c r="D31">
         <v>114</v>
       </c>
@@ -3390,7 +3444,7 @@
         <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D32">
         <v>21</v>
@@ -3425,7 +3479,7 @@
         <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D33">
         <v>19</v>
@@ -3456,6 +3510,9 @@
       <c r="A34" t="s">
         <v>17</v>
       </c>
+      <c r="B34" t="s">
+        <v>24</v>
+      </c>
       <c r="D34">
         <v>40</v>
       </c>
@@ -3489,7 +3546,7 @@
         <v>25</v>
       </c>
       <c r="C35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -3524,7 +3581,7 @@
         <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D36">
         <v>43</v>
@@ -3559,7 +3616,7 @@
         <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D37">
         <v>40</v>
@@ -3594,7 +3651,7 @@
         <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D38">
         <v>42</v>
@@ -3625,6 +3682,9 @@
       <c r="A39" t="s">
         <v>18</v>
       </c>
+      <c r="B39" t="s">
+        <v>24</v>
+      </c>
       <c r="D39">
         <v>159</v>
       </c>
@@ -3658,7 +3718,7 @@
         <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D40">
         <v>17</v>
@@ -3689,6 +3749,9 @@
       <c r="A41" t="s">
         <v>19</v>
       </c>
+      <c r="B41" t="s">
+        <v>24</v>
+      </c>
       <c r="D41">
         <v>17</v>
       </c>
@@ -3718,58 +3781,64 @@
       <c r="A42" t="s">
         <v>20</v>
       </c>
+      <c r="B42" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
+        <v>56</v>
+      </c>
       <c r="D42">
-        <v>1173</v>
+        <v>32</v>
       </c>
       <c r="E42">
-        <v>898</v>
+        <v>24</v>
       </c>
       <c r="F42">
-        <v>275</v>
+        <v>8</v>
       </c>
       <c r="G42" s="1">
-        <v>76.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="H42" s="1">
-        <v>23.4</v>
+        <v>25</v>
       </c>
       <c r="I42" s="2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="J42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B43" t="s">
         <v>23</v>
       </c>
       <c r="C43" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D43">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E43">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G43" s="1">
-        <v>75</v>
+        <v>76.7</v>
       </c>
       <c r="H43" s="1">
-        <v>25</v>
+        <v>23.3</v>
       </c>
       <c r="I43" s="2">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -3780,31 +3849,31 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D44">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E44">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F44">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G44" s="1">
-        <v>76.7</v>
+        <v>91.2</v>
       </c>
       <c r="H44" s="1">
-        <v>23.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I44" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -3815,31 +3884,31 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D45">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E45">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45" s="1">
-        <v>91.2</v>
+        <v>90</v>
       </c>
       <c r="H45" s="1">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I45" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -3850,31 +3919,31 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C46" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D46">
+        <v>28</v>
+      </c>
+      <c r="E46">
         <v>20</v>
       </c>
-      <c r="E46">
-        <v>18</v>
-      </c>
       <c r="F46">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G46" s="1">
-        <v>90</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H46" s="1">
-        <v>10</v>
+        <v>28.6</v>
       </c>
       <c r="I46" s="2">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -3885,31 +3954,28 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
         <v>24</v>
       </c>
-      <c r="C47" t="s">
-        <v>46</v>
-      </c>
       <c r="D47">
+        <v>144</v>
+      </c>
+      <c r="E47">
+        <v>116</v>
+      </c>
+      <c r="F47">
         <v>28</v>
       </c>
-      <c r="E47">
-        <v>20</v>
-      </c>
-      <c r="F47">
-        <v>8</v>
-      </c>
       <c r="G47" s="1">
-        <v>71.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H47" s="1">
-        <v>28.6</v>
+        <v>19.4</v>
       </c>
       <c r="I47" s="2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -3922,23 +3988,29 @@
       <c r="A48" t="s">
         <v>21</v>
       </c>
+      <c r="B48" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" t="s">
+        <v>58</v>
+      </c>
       <c r="D48">
-        <v>144</v>
+        <v>30</v>
       </c>
       <c r="E48">
-        <v>116</v>
+        <v>11</v>
       </c>
       <c r="F48">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G48" s="1">
-        <v>80.59999999999999</v>
+        <v>36.7</v>
       </c>
       <c r="H48" s="1">
-        <v>19.4</v>
+        <v>63.3</v>
       </c>
       <c r="I48" s="2">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -3949,31 +4021,31 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
         <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D49">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E49">
+        <v>22</v>
+      </c>
+      <c r="F49">
         <v>11</v>
       </c>
-      <c r="F49">
-        <v>19</v>
-      </c>
       <c r="G49" s="1">
-        <v>36.7</v>
+        <v>66.7</v>
       </c>
       <c r="H49" s="1">
-        <v>63.3</v>
+        <v>33.3</v>
       </c>
       <c r="I49" s="2">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -3984,31 +4056,31 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B50" t="s">
         <v>25</v>
       </c>
       <c r="C50" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D50">
         <v>33</v>
       </c>
       <c r="E50">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F50">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G50" s="1">
-        <v>66.7</v>
+        <v>54.5</v>
       </c>
       <c r="H50" s="1">
-        <v>33.3</v>
+        <v>45.5</v>
       </c>
       <c r="I50" s="2">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -4019,31 +4091,28 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
-      </c>
-      <c r="C51" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="D51">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="E51">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="F51">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G51" s="1">
-        <v>54.5</v>
+        <v>53.1</v>
       </c>
       <c r="H51" s="1">
-        <v>45.5</v>
+        <v>46.9</v>
       </c>
       <c r="I51" s="2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -4053,32 +4122,32 @@
       </c>
     </row>
     <row r="52" spans="1:11">
-      <c r="A52" t="s">
-        <v>22</v>
+      <c r="B52" t="s">
+        <v>27</v>
       </c>
       <c r="D52">
-        <v>96</v>
+        <v>1173</v>
       </c>
       <c r="E52">
-        <v>51</v>
+        <v>898</v>
       </c>
       <c r="F52">
-        <v>45</v>
+        <v>275</v>
       </c>
       <c r="G52" s="1">
-        <v>53.1</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="H52" s="1">
-        <v>46.9</v>
+        <v>23.4</v>
       </c>
       <c r="I52" s="2">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K52" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="Final" sheetId="2" r:id="rId2"/>
+    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="61">
   <si>
     <t>Docente</t>
   </si>
@@ -2418,6 +2419,1804 @@
         <v>27</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>27</v>
+      </c>
+      <c r="K2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>30</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>100</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>30</v>
+      </c>
+      <c r="K3" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4">
+        <v>26</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>26</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>100</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>26</v>
+      </c>
+      <c r="K4" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>17</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>17</v>
+      </c>
+      <c r="K5" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>19</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>19</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>119</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>119</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>100</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>119</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8">
+        <v>37</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>37</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>37</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9">
+        <v>31</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>31</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>31</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10">
+        <v>41</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>41</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>100</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>41</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11">
+        <v>31</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>31</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>31</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12">
+        <v>38</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>38</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>38</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13">
+        <v>28</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>28</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>100</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>28</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14">
+        <v>41</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>41</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>100</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>41</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15">
+        <v>247</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>247</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>247</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16">
+        <v>39</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>39</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>100</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>39</v>
+      </c>
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17">
+        <v>39</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>39</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>100</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>39</v>
+      </c>
+      <c r="K17" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18">
+        <v>36</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>36</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>100</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>36</v>
+      </c>
+      <c r="K18" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19">
+        <v>32</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>32</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>100</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>32</v>
+      </c>
+      <c r="K19" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20">
+        <v>21</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>21</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>100</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>21</v>
+      </c>
+      <c r="K20" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21">
+        <v>31</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>31</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>100</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>31</v>
+      </c>
+      <c r="K21" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22">
+        <v>120</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>120</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>100</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>120</v>
+      </c>
+      <c r="K22" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23">
+        <v>30</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>30</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>100</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>30</v>
+      </c>
+      <c r="K23" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24">
+        <v>20</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>20</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>100</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>20</v>
+      </c>
+      <c r="K24" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25">
+        <v>28</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>28</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>100</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>28</v>
+      </c>
+      <c r="K25" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26">
+        <v>78</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>78</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>100</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>78</v>
+      </c>
+      <c r="K26" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27">
+        <v>41</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>41</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>100</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>41</v>
+      </c>
+      <c r="K27" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28">
+        <v>34</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>34</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>100</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>34</v>
+      </c>
+      <c r="K28" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29">
+        <v>25</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>25</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>100</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>25</v>
+      </c>
+      <c r="K29" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30">
+        <v>14</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>14</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>100</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>14</v>
+      </c>
+      <c r="K30" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31">
+        <v>114</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>114</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>100</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>114</v>
+      </c>
+      <c r="K31" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32">
+        <v>21</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>21</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>100</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>21</v>
+      </c>
+      <c r="K32" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33">
+        <v>19</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>19</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>100</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>19</v>
+      </c>
+      <c r="K33" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34">
+        <v>40</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>40</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>100</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>40</v>
+      </c>
+      <c r="K34" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35">
+        <v>34</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>34</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>100</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>34</v>
+      </c>
+      <c r="K35" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36">
+        <v>43</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>43</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>100</v>
+      </c>
+      <c r="I36" s="2">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>43</v>
+      </c>
+      <c r="K36" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37">
+        <v>40</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>40</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>100</v>
+      </c>
+      <c r="I37" s="2">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>40</v>
+      </c>
+      <c r="K37" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38">
+        <v>42</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>42</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>100</v>
+      </c>
+      <c r="I38" s="2">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>42</v>
+      </c>
+      <c r="K38" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39">
+        <v>159</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>159</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>100</v>
+      </c>
+      <c r="I39" s="2">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>159</v>
+      </c>
+      <c r="K39" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40">
+        <v>17</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>17</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>100</v>
+      </c>
+      <c r="I40" s="2">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>17</v>
+      </c>
+      <c r="K40" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41">
+        <v>17</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>17</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>100</v>
+      </c>
+      <c r="I41" s="2">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>17</v>
+      </c>
+      <c r="K41" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42">
+        <v>32</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>32</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>100</v>
+      </c>
+      <c r="I42" s="2">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>32</v>
+      </c>
+      <c r="K42" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43">
+        <v>30</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>30</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>100</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>30</v>
+      </c>
+      <c r="K43" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
+        <v>20</v>
+      </c>
+      <c r="B44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" t="s">
+        <v>57</v>
+      </c>
+      <c r="D44">
+        <v>34</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>34</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>100</v>
+      </c>
+      <c r="I44" s="2">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>34</v>
+      </c>
+      <c r="K44" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B45" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45">
+        <v>20</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>20</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>100</v>
+      </c>
+      <c r="I45" s="2">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>20</v>
+      </c>
+      <c r="K45" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
+        <v>20</v>
+      </c>
+      <c r="B46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C46" t="s">
+        <v>47</v>
+      </c>
+      <c r="D46">
+        <v>28</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>28</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>100</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>28</v>
+      </c>
+      <c r="K46" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" t="s">
+        <v>20</v>
+      </c>
+      <c r="B47" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47">
+        <v>144</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>144</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>100</v>
+      </c>
+      <c r="I47" s="2">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>144</v>
+      </c>
+      <c r="K47" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" t="s">
+        <v>58</v>
+      </c>
+      <c r="D48">
+        <v>30</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>30</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>100</v>
+      </c>
+      <c r="I48" s="2">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>30</v>
+      </c>
+      <c r="K48" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" t="s">
+        <v>59</v>
+      </c>
+      <c r="D49">
+        <v>33</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>33</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>100</v>
+      </c>
+      <c r="I49" s="2">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>33</v>
+      </c>
+      <c r="K49" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" t="s">
+        <v>21</v>
+      </c>
+      <c r="B50" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50">
+        <v>33</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>33</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>100</v>
+      </c>
+      <c r="I50" s="2">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>33</v>
+      </c>
+      <c r="K50" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
+        <v>21</v>
+      </c>
+      <c r="B51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51">
+        <v>96</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>96</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>100</v>
+      </c>
+      <c r="I51" s="2">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>96</v>
+      </c>
+      <c r="K51" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="B52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52">
+        <v>1173</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>1173</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>100</v>
+      </c>
+      <c r="I52" s="2">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1173</v>
+      </c>
+      <c r="K52" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K52"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2">
+        <v>27</v>
+      </c>
+      <c r="E2">
         <v>18</v>
       </c>
       <c r="F2">

--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -2233,28 +2233,28 @@
         <v>59</v>
       </c>
       <c r="D49">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E49">
         <v>22</v>
       </c>
       <c r="F49">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G49" s="1">
-        <v>66.7</v>
+        <v>64.7</v>
       </c>
       <c r="H49" s="1">
-        <v>33.3</v>
+        <v>35.3</v>
       </c>
       <c r="I49" s="2">
         <v>6.8</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2300,28 +2300,28 @@
         <v>24</v>
       </c>
       <c r="D51">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E51">
         <v>51</v>
       </c>
       <c r="F51">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G51" s="1">
-        <v>53.1</v>
+        <v>52.6</v>
       </c>
       <c r="H51" s="1">
-        <v>46.9</v>
+        <v>47.4</v>
       </c>
       <c r="I51" s="2">
         <v>5.9</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2329,28 +2329,28 @@
         <v>27</v>
       </c>
       <c r="D52">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="E52">
         <v>898</v>
       </c>
       <c r="F52">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G52" s="1">
-        <v>76.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="H52" s="1">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="I52" s="2">
         <v>6.9</v>
       </c>
       <c r="J52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K52" s="1">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -2696,25 +2696,25 @@
         <v>41</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>46.3</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>53.7</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2731,25 +2731,25 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>54.8</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>45.2</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J11">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2766,25 +2766,25 @@
         <v>38</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>86.8</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>13.2</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J12">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2801,25 +2801,25 @@
         <v>28</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F13">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>64.3</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>35.7</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J13">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2836,25 +2836,25 @@
         <v>41</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>58.5</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>41.5</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2868,25 +2868,25 @@
         <v>247</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="F15">
-        <v>247</v>
+        <v>136</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>44.9</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>55.1</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J15">
-        <v>247</v>
+        <v>68</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2970,25 +2970,25 @@
         <v>36</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F18">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3005,25 +3005,25 @@
         <v>32</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F19">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J19">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3107,25 +3107,25 @@
         <v>120</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="F22">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>54.2</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>45.8</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J22">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -3451,25 +3451,25 @@
         <v>21</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F32">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>52.4</v>
       </c>
       <c r="H32" s="1">
-        <v>100</v>
+        <v>47.6</v>
       </c>
       <c r="I32" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J32">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3486,25 +3486,25 @@
         <v>19</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F33">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>57.9</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>42.1</v>
       </c>
       <c r="I33" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J33">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3518,25 +3518,25 @@
         <v>40</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F34">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H34" s="1">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="I34" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J34">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -3725,25 +3725,25 @@
         <v>17</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F40">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H40" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I40" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J40">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -3757,25 +3757,25 @@
         <v>17</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F41">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H41" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I41" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J41">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -4031,13 +4031,13 @@
         <v>59</v>
       </c>
       <c r="D49">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E49">
         <v>0</v>
       </c>
       <c r="F49">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G49" s="1">
         <v>0</v>
@@ -4049,7 +4049,7 @@
         <v>0</v>
       </c>
       <c r="J49">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K49" s="1">
         <v>100</v>
@@ -4098,13 +4098,13 @@
         <v>24</v>
       </c>
       <c r="D51">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G51" s="1">
         <v>0</v>
@@ -4116,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="J51">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K51" s="1">
         <v>100</v>
@@ -4127,28 +4127,28 @@
         <v>27</v>
       </c>
       <c r="D52">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="F52">
-        <v>1173</v>
+        <v>959</v>
       </c>
       <c r="G52" s="1">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="H52" s="1">
-        <v>100</v>
+        <v>81.7</v>
       </c>
       <c r="I52" s="2">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J52">
-        <v>1173</v>
+        <v>873</v>
       </c>
       <c r="K52" s="1">
-        <v>100</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4494,19 +4494,19 @@
         <v>41</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G10" s="1">
-        <v>58.5</v>
+        <v>46.3</v>
       </c>
       <c r="H10" s="1">
-        <v>41.5</v>
+        <v>53.7</v>
       </c>
       <c r="I10" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -4529,19 +4529,19 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G11" s="1">
-        <v>74.2</v>
+        <v>54.8</v>
       </c>
       <c r="H11" s="1">
-        <v>25.8</v>
+        <v>45.2</v>
       </c>
       <c r="I11" s="2">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -4564,16 +4564,16 @@
         <v>38</v>
       </c>
       <c r="E12">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>92.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="H12" s="1">
-        <v>7.9</v>
+        <v>13.2</v>
       </c>
       <c r="I12" s="2">
         <v>7.3</v>
@@ -4611,7 +4611,7 @@
         <v>35.7</v>
       </c>
       <c r="I13" s="2">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -4634,19 +4634,19 @@
         <v>41</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G14" s="1">
-        <v>68.3</v>
+        <v>58.5</v>
       </c>
       <c r="H14" s="1">
-        <v>31.7</v>
+        <v>41.5</v>
       </c>
       <c r="I14" s="2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -4666,16 +4666,16 @@
         <v>247</v>
       </c>
       <c r="E15">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="F15">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="G15" s="1">
-        <v>67.2</v>
+        <v>60.3</v>
       </c>
       <c r="H15" s="1">
-        <v>32.8</v>
+        <v>39.7</v>
       </c>
       <c r="I15" s="2">
         <v>6.2</v>
@@ -4768,19 +4768,19 @@
         <v>36</v>
       </c>
       <c r="E18">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>83.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>16.7</v>
+        <v>5.6</v>
       </c>
       <c r="I18" s="2">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4815,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4905,19 +4905,19 @@
         <v>120</v>
       </c>
       <c r="E22">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F22">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G22" s="1">
-        <v>89.2</v>
+        <v>92.5</v>
       </c>
       <c r="H22" s="1">
-        <v>10.8</v>
+        <v>7.5</v>
       </c>
       <c r="I22" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -5249,16 +5249,16 @@
         <v>21</v>
       </c>
       <c r="E32">
+        <v>11</v>
+      </c>
+      <c r="F32">
         <v>10</v>
       </c>
-      <c r="F32">
-        <v>11</v>
-      </c>
       <c r="G32" s="1">
+        <v>52.4</v>
+      </c>
+      <c r="H32" s="1">
         <v>47.6</v>
-      </c>
-      <c r="H32" s="1">
-        <v>52.4</v>
       </c>
       <c r="I32" s="2">
         <v>5.9</v>
@@ -5284,19 +5284,19 @@
         <v>19</v>
       </c>
       <c r="E33">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G33" s="1">
-        <v>78.90000000000001</v>
+        <v>57.9</v>
       </c>
       <c r="H33" s="1">
-        <v>21.1</v>
+        <v>42.1</v>
       </c>
       <c r="I33" s="2">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -5316,19 +5316,19 @@
         <v>40</v>
       </c>
       <c r="E34">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F34">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G34" s="1">
-        <v>62.5</v>
+        <v>55</v>
       </c>
       <c r="H34" s="1">
-        <v>37.5</v>
+        <v>45</v>
       </c>
       <c r="I34" s="2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -5535,7 +5535,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="2">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -5567,7 +5567,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="2">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -5829,28 +5829,28 @@
         <v>59</v>
       </c>
       <c r="D49">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E49">
         <v>22</v>
       </c>
       <c r="F49">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G49" s="1">
-        <v>66.7</v>
+        <v>64.7</v>
       </c>
       <c r="H49" s="1">
-        <v>33.3</v>
+        <v>35.3</v>
       </c>
       <c r="I49" s="2">
         <v>6.9</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" s="1">
-        <v>0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -5896,28 +5896,28 @@
         <v>24</v>
       </c>
       <c r="D51">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E51">
         <v>51</v>
       </c>
       <c r="F51">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G51" s="1">
-        <v>53.1</v>
+        <v>52.6</v>
       </c>
       <c r="H51" s="1">
-        <v>46.9</v>
+        <v>47.4</v>
       </c>
       <c r="I51" s="2">
         <v>6.2</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -5925,28 +5925,28 @@
         <v>27</v>
       </c>
       <c r="D52">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="E52">
-        <v>898</v>
+        <v>882</v>
       </c>
       <c r="F52">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="G52" s="1">
-        <v>76.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H52" s="1">
-        <v>23.4</v>
+        <v>24.9</v>
       </c>
       <c r="I52" s="2">
         <v>7</v>
       </c>
       <c r="J52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K52" s="1">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -668,13 +668,13 @@
         <v>60</v>
       </c>
       <c r="I3" s="2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -808,10 +808,10 @@
         <v>6.9</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1516,25 +1516,25 @@
         <v>34</v>
       </c>
       <c r="E28">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28" s="1">
-        <v>73.5</v>
+        <v>76.5</v>
       </c>
       <c r="H28" s="1">
-        <v>26.5</v>
+        <v>23.5</v>
       </c>
       <c r="I28" s="2">
         <v>6.9</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1618,25 +1618,25 @@
         <v>114</v>
       </c>
       <c r="E31">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F31">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G31" s="1">
-        <v>78.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>21.9</v>
+        <v>21.1</v>
       </c>
       <c r="I31" s="2">
         <v>7.1</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2332,25 +2332,25 @@
         <v>1174</v>
       </c>
       <c r="E52">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="F52">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G52" s="1">
-        <v>76.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="H52" s="1">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="I52" s="2">
         <v>6.9</v>
       </c>
       <c r="J52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K52" s="1">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -2454,25 +2454,25 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>53.3</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2524,25 +2524,25 @@
         <v>17</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>29.4</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2559,25 +2559,25 @@
         <v>19</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>21.1</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2591,25 +2591,25 @@
         <v>119</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F7">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>65.5</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J7">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2626,25 +2626,25 @@
         <v>37</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>59.5</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>40.5</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J8">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2661,25 +2661,25 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F9">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>35.5</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>64.5</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="J9">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2868,25 +2868,25 @@
         <v>247</v>
       </c>
       <c r="E15">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="F15">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="G15" s="1">
-        <v>44.9</v>
+        <v>58.3</v>
       </c>
       <c r="H15" s="1">
-        <v>55.1</v>
+        <v>41.7</v>
       </c>
       <c r="I15" s="2">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="J15">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>27.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2903,25 +2903,25 @@
         <v>39</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F16">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>43.6</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J16">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2935,25 +2935,25 @@
         <v>39</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F17">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>43.6</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J17">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2970,25 +2970,25 @@
         <v>36</v>
       </c>
       <c r="E18">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3040,25 +3040,25 @@
         <v>21</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F20">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J20">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -3107,25 +3107,25 @@
         <v>120</v>
       </c>
       <c r="E22">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="F22">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="G22" s="1">
-        <v>54.2</v>
+        <v>69.2</v>
       </c>
       <c r="H22" s="1">
-        <v>45.8</v>
+        <v>30.8</v>
       </c>
       <c r="I22" s="2">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="J22">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="K22" s="1">
-        <v>45.8</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -3279,25 +3279,25 @@
         <v>41</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F27">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>4.9</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J27">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3314,25 +3314,25 @@
         <v>34</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F28">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>32.4</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J28">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3349,25 +3349,25 @@
         <v>25</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F29">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3384,25 +3384,25 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J30">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -3416,25 +3416,25 @@
         <v>114</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="F31">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>77.2</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>22.8</v>
       </c>
       <c r="I31" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4130,25 +4130,25 @@
         <v>1174</v>
       </c>
       <c r="E52">
-        <v>215</v>
+        <v>417</v>
       </c>
       <c r="F52">
-        <v>959</v>
+        <v>757</v>
       </c>
       <c r="G52" s="1">
-        <v>18.3</v>
+        <v>35.5</v>
       </c>
       <c r="H52" s="1">
-        <v>81.7</v>
+        <v>64.5</v>
       </c>
       <c r="I52" s="2">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J52">
-        <v>873</v>
+        <v>566</v>
       </c>
       <c r="K52" s="1">
-        <v>74.40000000000001</v>
+        <v>48.2</v>
       </c>
     </row>
   </sheetData>
@@ -4252,25 +4252,25 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1">
-        <v>40</v>
+        <v>46.7</v>
       </c>
       <c r="H3" s="1">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="I3" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -4322,19 +4322,19 @@
         <v>17</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>11.8</v>
+        <v>5.9</v>
       </c>
       <c r="I5" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -4357,19 +4357,19 @@
         <v>19</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>89.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>10.5</v>
+        <v>21.1</v>
       </c>
       <c r="I6" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -4389,25 +4389,25 @@
         <v>119</v>
       </c>
       <c r="E7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G7" s="1">
-        <v>71.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="H7" s="1">
-        <v>28.6</v>
+        <v>27.7</v>
       </c>
       <c r="I7" s="2">
         <v>7</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -4424,19 +4424,19 @@
         <v>37</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1">
-        <v>62.2</v>
+        <v>59.5</v>
       </c>
       <c r="H8" s="1">
-        <v>37.8</v>
+        <v>40.5</v>
       </c>
       <c r="I8" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -4459,19 +4459,19 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F9">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G9" s="1">
-        <v>48.4</v>
+        <v>35.5</v>
       </c>
       <c r="H9" s="1">
-        <v>51.6</v>
+        <v>64.5</v>
       </c>
       <c r="I9" s="2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -4666,16 +4666,16 @@
         <v>247</v>
       </c>
       <c r="E15">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F15">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G15" s="1">
-        <v>60.3</v>
+        <v>58.3</v>
       </c>
       <c r="H15" s="1">
-        <v>39.7</v>
+        <v>41.7</v>
       </c>
       <c r="I15" s="2">
         <v>6.2</v>
@@ -4701,16 +4701,16 @@
         <v>39</v>
       </c>
       <c r="E16">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G16" s="1">
-        <v>74.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="H16" s="1">
-        <v>25.6</v>
+        <v>43.6</v>
       </c>
       <c r="I16" s="2">
         <v>6.5</v>
@@ -4733,16 +4733,16 @@
         <v>39</v>
       </c>
       <c r="E17">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G17" s="1">
-        <v>74.40000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="H17" s="1">
-        <v>25.6</v>
+        <v>43.6</v>
       </c>
       <c r="I17" s="2">
         <v>6.5</v>
@@ -4768,16 +4768,16 @@
         <v>36</v>
       </c>
       <c r="E18">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
         <v>8.6</v>
@@ -4838,16 +4838,16 @@
         <v>21</v>
       </c>
       <c r="E20">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G20" s="1">
-        <v>66.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>33.3</v>
+        <v>28.6</v>
       </c>
       <c r="I20" s="2">
         <v>7</v>
@@ -4905,16 +4905,16 @@
         <v>120</v>
       </c>
       <c r="E22">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F22">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G22" s="1">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="H22" s="1">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="I22" s="2">
         <v>8</v>
@@ -5077,19 +5077,19 @@
         <v>41</v>
       </c>
       <c r="E27">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G27" s="1">
-        <v>90.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="I27" s="2">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -5112,25 +5112,25 @@
         <v>34</v>
       </c>
       <c r="E28">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F28">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G28" s="1">
-        <v>73.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H28" s="1">
-        <v>26.5</v>
+        <v>32.4</v>
       </c>
       <c r="I28" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -5147,19 +5147,19 @@
         <v>25</v>
       </c>
       <c r="E29">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G29" s="1">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H29" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I29" s="2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -5194,7 +5194,7 @@
         <v>28.6</v>
       </c>
       <c r="I30" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -5214,25 +5214,25 @@
         <v>114</v>
       </c>
       <c r="E31">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F31">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G31" s="1">
-        <v>78.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="H31" s="1">
-        <v>21.9</v>
+        <v>22.8</v>
       </c>
       <c r="I31" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -5928,25 +5928,25 @@
         <v>1174</v>
       </c>
       <c r="E52">
-        <v>882</v>
+        <v>873</v>
       </c>
       <c r="F52">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="G52" s="1">
-        <v>75.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H52" s="1">
-        <v>24.9</v>
+        <v>25.6</v>
       </c>
       <c r="I52" s="2">
         <v>7</v>
       </c>
       <c r="J52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K52" s="1">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -2236,25 +2236,25 @@
         <v>34</v>
       </c>
       <c r="E49">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F49">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G49" s="1">
-        <v>64.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H49" s="1">
-        <v>35.3</v>
+        <v>32.4</v>
       </c>
       <c r="I49" s="2">
         <v>6.8</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2303,25 +2303,25 @@
         <v>97</v>
       </c>
       <c r="E51">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F51">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G51" s="1">
-        <v>52.6</v>
+        <v>53.6</v>
       </c>
       <c r="H51" s="1">
-        <v>47.4</v>
+        <v>46.4</v>
       </c>
       <c r="I51" s="2">
         <v>5.9</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2332,25 +2332,25 @@
         <v>1174</v>
       </c>
       <c r="E52">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="F52">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G52" s="1">
-        <v>76.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="H52" s="1">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="I52" s="2">
         <v>6.9</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3827,25 +3827,25 @@
         <v>30</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F43">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H43" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I43" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J43">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -3862,25 +3862,25 @@
         <v>34</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F44">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H44" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I44" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J44">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -3932,25 +3932,25 @@
         <v>28</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F46">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G46" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H46" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I46" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J46">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -3964,25 +3964,25 @@
         <v>144</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F47">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="G47" s="1">
-        <v>0</v>
+        <v>54.2</v>
       </c>
       <c r="H47" s="1">
-        <v>100</v>
+        <v>45.8</v>
       </c>
       <c r="I47" s="2">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="J47">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="K47" s="1">
-        <v>100</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -3999,25 +3999,25 @@
         <v>30</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F48">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>36.7</v>
       </c>
       <c r="H48" s="1">
-        <v>100</v>
+        <v>63.3</v>
       </c>
       <c r="I48" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J48">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K48" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -4034,25 +4034,25 @@
         <v>34</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F49">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="G49" s="1">
-        <v>0</v>
+        <v>76.5</v>
       </c>
       <c r="H49" s="1">
-        <v>100</v>
+        <v>23.5</v>
       </c>
       <c r="I49" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J49">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -4069,25 +4069,25 @@
         <v>33</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F50">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G50" s="1">
-        <v>0</v>
+        <v>63.6</v>
       </c>
       <c r="H50" s="1">
-        <v>100</v>
+        <v>36.4</v>
       </c>
       <c r="I50" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J50">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -4101,25 +4101,25 @@
         <v>97</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F51">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="G51" s="1">
-        <v>0</v>
+        <v>59.8</v>
       </c>
       <c r="H51" s="1">
-        <v>100</v>
+        <v>40.2</v>
       </c>
       <c r="I51" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J51">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -4130,25 +4130,25 @@
         <v>1174</v>
       </c>
       <c r="E52">
-        <v>417</v>
+        <v>553</v>
       </c>
       <c r="F52">
-        <v>757</v>
+        <v>621</v>
       </c>
       <c r="G52" s="1">
-        <v>35.5</v>
+        <v>47.1</v>
       </c>
       <c r="H52" s="1">
-        <v>64.5</v>
+        <v>52.9</v>
       </c>
       <c r="I52" s="2">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="J52">
-        <v>566</v>
+        <v>377</v>
       </c>
       <c r="K52" s="1">
-        <v>48.2</v>
+        <v>32.1</v>
       </c>
     </row>
   </sheetData>
@@ -5625,19 +5625,19 @@
         <v>30</v>
       </c>
       <c r="E43">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G43" s="1">
-        <v>76.7</v>
+        <v>80</v>
       </c>
       <c r="H43" s="1">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="I43" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -5660,19 +5660,19 @@
         <v>34</v>
       </c>
       <c r="E44">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>91.2</v>
+        <v>100</v>
       </c>
       <c r="H44" s="1">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="I44" s="2">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -5762,19 +5762,19 @@
         <v>144</v>
       </c>
       <c r="E47">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F47">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G47" s="1">
-        <v>80.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="H47" s="1">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="I47" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -5809,7 +5809,7 @@
         <v>63.3</v>
       </c>
       <c r="I48" s="2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -5832,25 +5832,25 @@
         <v>34</v>
       </c>
       <c r="E49">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F49">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G49" s="1">
-        <v>64.7</v>
+        <v>76.5</v>
       </c>
       <c r="H49" s="1">
-        <v>35.3</v>
+        <v>23.5</v>
       </c>
       <c r="I49" s="2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -5867,19 +5867,19 @@
         <v>33</v>
       </c>
       <c r="E50">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F50">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G50" s="1">
-        <v>54.5</v>
+        <v>63.6</v>
       </c>
       <c r="H50" s="1">
-        <v>45.5</v>
+        <v>36.4</v>
       </c>
       <c r="I50" s="2">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -5899,25 +5899,25 @@
         <v>97</v>
       </c>
       <c r="E51">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F51">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G51" s="1">
-        <v>52.6</v>
+        <v>59.8</v>
       </c>
       <c r="H51" s="1">
-        <v>47.4</v>
+        <v>40.2</v>
       </c>
       <c r="I51" s="2">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -5928,25 +5928,25 @@
         <v>1174</v>
       </c>
       <c r="E52">
-        <v>873</v>
+        <v>884</v>
       </c>
       <c r="F52">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="G52" s="1">
-        <v>74.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="H52" s="1">
-        <v>25.6</v>
+        <v>24.7</v>
       </c>
       <c r="I52" s="2">
         <v>7</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -2419,25 +2419,25 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>59.3</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>40.7</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2489,25 +2489,25 @@
         <v>26</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>26.9</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2524,25 +2524,25 @@
         <v>17</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>70.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>29.4</v>
+        <v>5.9</v>
       </c>
       <c r="I5" s="2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>23.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2591,25 +2591,25 @@
         <v>119</v>
       </c>
       <c r="E7">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="F7">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="G7" s="1">
-        <v>34.5</v>
+        <v>67.2</v>
       </c>
       <c r="H7" s="1">
-        <v>65.5</v>
+        <v>32.8</v>
       </c>
       <c r="I7" s="2">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>47.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3142,25 +3142,25 @@
         <v>30</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F23">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J23">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -3177,25 +3177,25 @@
         <v>20</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F24">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J24">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3212,25 +3212,25 @@
         <v>28</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J25">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -3244,25 +3244,25 @@
         <v>78</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F26">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J26">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -3897,25 +3897,25 @@
         <v>20</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F45">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G45" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H45" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I45" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J45">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -3964,25 +3964,25 @@
         <v>144</v>
       </c>
       <c r="E47">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="F47">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="G47" s="1">
-        <v>54.2</v>
+        <v>66.7</v>
       </c>
       <c r="H47" s="1">
-        <v>45.8</v>
+        <v>33.3</v>
       </c>
       <c r="I47" s="2">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="J47">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="K47" s="1">
-        <v>36.1</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -4130,25 +4130,25 @@
         <v>1174</v>
       </c>
       <c r="E52">
-        <v>553</v>
+        <v>688</v>
       </c>
       <c r="F52">
-        <v>621</v>
+        <v>486</v>
       </c>
       <c r="G52" s="1">
-        <v>47.1</v>
+        <v>58.6</v>
       </c>
       <c r="H52" s="1">
-        <v>52.9</v>
+        <v>41.4</v>
       </c>
       <c r="I52" s="2">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="J52">
-        <v>377</v>
+        <v>222</v>
       </c>
       <c r="K52" s="1">
-        <v>32.1</v>
+        <v>18.9</v>
       </c>
     </row>
   </sheetData>
@@ -4217,19 +4217,19 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1">
-        <v>66.7</v>
+        <v>59.3</v>
       </c>
       <c r="H2" s="1">
-        <v>33.3</v>
+        <v>40.7</v>
       </c>
       <c r="I2" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -4287,19 +4287,19 @@
         <v>26</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>88.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>11.5</v>
+        <v>26.9</v>
       </c>
       <c r="I4" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -4389,16 +4389,16 @@
         <v>119</v>
       </c>
       <c r="E7">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G7" s="1">
-        <v>72.3</v>
+        <v>67.2</v>
       </c>
       <c r="H7" s="1">
-        <v>27.7</v>
+        <v>32.8</v>
       </c>
       <c r="I7" s="2">
         <v>7</v>
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4987,7 +4987,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -5022,7 +5022,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -5054,7 +5054,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -5928,16 +5928,16 @@
         <v>1174</v>
       </c>
       <c r="E52">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="F52">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="G52" s="1">
-        <v>75.3</v>
+        <v>74.8</v>
       </c>
       <c r="H52" s="1">
-        <v>24.7</v>
+        <v>25.2</v>
       </c>
       <c r="I52" s="2">
         <v>7</v>

--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -3075,25 +3075,25 @@
         <v>31</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F21">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>12.9</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J21">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -3107,25 +3107,25 @@
         <v>120</v>
       </c>
       <c r="E22">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="F22">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G22" s="1">
-        <v>69.2</v>
+        <v>91.7</v>
       </c>
       <c r="H22" s="1">
-        <v>30.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="2">
-        <v>6.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J22">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>25.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -3553,25 +3553,25 @@
         <v>34</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F35">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H35" s="1">
-        <v>100</v>
+        <v>20.6</v>
       </c>
       <c r="I35" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J35">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3588,25 +3588,25 @@
         <v>43</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F36">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H36" s="1">
-        <v>100</v>
+        <v>18.6</v>
       </c>
       <c r="I36" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J36">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -3623,25 +3623,25 @@
         <v>40</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F37">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H37" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="I37" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J37">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3658,25 +3658,25 @@
         <v>42</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F38">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H38" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I38" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J38">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3690,25 +3690,25 @@
         <v>159</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F39">
-        <v>159</v>
+        <v>39</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>75.5</v>
       </c>
       <c r="H39" s="1">
-        <v>100</v>
+        <v>24.5</v>
       </c>
       <c r="I39" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J39">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -3792,25 +3792,25 @@
         <v>32</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F42">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H42" s="1">
-        <v>100</v>
+        <v>21.9</v>
       </c>
       <c r="I42" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J42">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -3964,25 +3964,25 @@
         <v>144</v>
       </c>
       <c r="E47">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="F47">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="G47" s="1">
-        <v>66.7</v>
+        <v>84</v>
       </c>
       <c r="H47" s="1">
-        <v>33.3</v>
+        <v>16</v>
       </c>
       <c r="I47" s="2">
-        <v>5.7</v>
+        <v>7.1</v>
       </c>
       <c r="J47">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K47" s="1">
-        <v>22.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -4130,25 +4130,25 @@
         <v>1174</v>
       </c>
       <c r="E52">
-        <v>688</v>
+        <v>860</v>
       </c>
       <c r="F52">
-        <v>486</v>
+        <v>314</v>
       </c>
       <c r="G52" s="1">
-        <v>58.6</v>
+        <v>73.3</v>
       </c>
       <c r="H52" s="1">
-        <v>41.4</v>
+        <v>26.7</v>
       </c>
       <c r="I52" s="2">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="J52">
-        <v>222</v>
+        <v>1</v>
       </c>
       <c r="K52" s="1">
-        <v>18.9</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -4873,19 +4873,19 @@
         <v>31</v>
       </c>
       <c r="E21">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G21" s="1">
-        <v>100</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="I21" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4905,19 +4905,19 @@
         <v>120</v>
       </c>
       <c r="E22">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G22" s="1">
-        <v>95</v>
+        <v>91.7</v>
       </c>
       <c r="H22" s="1">
-        <v>5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -5351,19 +5351,19 @@
         <v>34</v>
       </c>
       <c r="E35">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G35" s="1">
-        <v>88.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H35" s="1">
-        <v>11.8</v>
+        <v>20.6</v>
       </c>
       <c r="I35" s="2">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -5386,19 +5386,19 @@
         <v>43</v>
       </c>
       <c r="E36">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G36" s="1">
-        <v>86</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H36" s="1">
-        <v>14</v>
+        <v>18.6</v>
       </c>
       <c r="I36" s="2">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -5421,19 +5421,19 @@
         <v>40</v>
       </c>
       <c r="E37">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G37" s="1">
-        <v>87.5</v>
+        <v>70</v>
       </c>
       <c r="H37" s="1">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="I37" s="2">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -5456,19 +5456,19 @@
         <v>42</v>
       </c>
       <c r="E38">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F38">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G38" s="1">
-        <v>78.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H38" s="1">
-        <v>21.4</v>
+        <v>28.6</v>
       </c>
       <c r="I38" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -5488,19 +5488,19 @@
         <v>159</v>
       </c>
       <c r="E39">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="F39">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G39" s="1">
-        <v>84.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="H39" s="1">
-        <v>15.1</v>
+        <v>24.5</v>
       </c>
       <c r="I39" s="2">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -5590,19 +5590,19 @@
         <v>32</v>
       </c>
       <c r="E42">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G42" s="1">
-        <v>75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H42" s="1">
-        <v>25</v>
+        <v>21.9</v>
       </c>
       <c r="I42" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -5762,16 +5762,16 @@
         <v>144</v>
       </c>
       <c r="E47">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F47">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G47" s="1">
-        <v>83.3</v>
+        <v>84</v>
       </c>
       <c r="H47" s="1">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="I47" s="2">
         <v>7.3</v>
@@ -5928,16 +5928,16 @@
         <v>1174</v>
       </c>
       <c r="E52">
-        <v>878</v>
+        <v>860</v>
       </c>
       <c r="F52">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="G52" s="1">
-        <v>74.8</v>
+        <v>73.3</v>
       </c>
       <c r="H52" s="1">
-        <v>25.2</v>
+        <v>26.7</v>
       </c>
       <c r="I52" s="2">
         <v>7</v>

--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -3670,13 +3670,13 @@
         <v>28.6</v>
       </c>
       <c r="I38" s="2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>2.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3702,13 +3702,13 @@
         <v>24.5</v>
       </c>
       <c r="I39" s="2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -4142,13 +4142,13 @@
         <v>26.7</v>
       </c>
       <c r="I52" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -2363,8 +2363,7 @@
   <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -4161,8 +4160,7 @@
   <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -4217,19 +4215,19 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>59.3</v>
+        <v>85.2</v>
       </c>
       <c r="H2" s="1">
-        <v>40.7</v>
+        <v>14.8</v>
       </c>
       <c r="I2" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -4252,16 +4250,16 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="H3" s="1">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="I3" s="2">
         <v>6.3</v>
@@ -4287,19 +4285,19 @@
         <v>26</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>73.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="H4" s="1">
-        <v>26.9</v>
+        <v>3.8</v>
       </c>
       <c r="I4" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -4334,7 +4332,7 @@
         <v>5.9</v>
       </c>
       <c r="I5" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -4357,16 +4355,16 @@
         <v>19</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>78.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="H6" s="1">
-        <v>21.1</v>
+        <v>10.5</v>
       </c>
       <c r="I6" s="2">
         <v>7.1</v>
@@ -4389,16 +4387,16 @@
         <v>119</v>
       </c>
       <c r="E7">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="F7">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G7" s="1">
-        <v>67.2</v>
+        <v>80.7</v>
       </c>
       <c r="H7" s="1">
-        <v>32.8</v>
+        <v>19.3</v>
       </c>
       <c r="I7" s="2">
         <v>7</v>
@@ -4701,19 +4699,19 @@
         <v>39</v>
       </c>
       <c r="E16">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F16">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G16" s="1">
-        <v>56.4</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>43.6</v>
+        <v>15.4</v>
       </c>
       <c r="I16" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -4733,19 +4731,19 @@
         <v>39</v>
       </c>
       <c r="E17">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F17">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>56.4</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>43.6</v>
+        <v>15.4</v>
       </c>
       <c r="I17" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4780,7 +4778,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4815,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4838,19 +4836,19 @@
         <v>21</v>
       </c>
       <c r="E20">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G20" s="1">
-        <v>71.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H20" s="1">
-        <v>28.6</v>
+        <v>14.3</v>
       </c>
       <c r="I20" s="2">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4873,19 +4871,19 @@
         <v>31</v>
       </c>
       <c r="E21">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>87.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4905,19 +4903,19 @@
         <v>120</v>
       </c>
       <c r="E22">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>91.7</v>
+        <v>97.5</v>
       </c>
       <c r="H22" s="1">
-        <v>8.300000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="I22" s="2">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4940,16 +4938,16 @@
         <v>30</v>
       </c>
       <c r="E23">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I23" s="2">
         <v>7.4</v>
@@ -4975,19 +4973,19 @@
         <v>20</v>
       </c>
       <c r="E24">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I24" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -5010,19 +5008,19 @@
         <v>28</v>
       </c>
       <c r="E25">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I25" s="2">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -5042,19 +5040,19 @@
         <v>78</v>
       </c>
       <c r="E26">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G26" s="1">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="I26" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -5089,7 +5087,7 @@
         <v>4.9</v>
       </c>
       <c r="I27" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -5112,16 +5110,16 @@
         <v>34</v>
       </c>
       <c r="E28">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F28">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G28" s="1">
-        <v>67.59999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="H28" s="1">
-        <v>32.4</v>
+        <v>14.7</v>
       </c>
       <c r="I28" s="2">
         <v>6.7</v>
@@ -5147,19 +5145,19 @@
         <v>25</v>
       </c>
       <c r="E29">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G29" s="1">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H29" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I29" s="2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -5194,7 +5192,7 @@
         <v>28.6</v>
       </c>
       <c r="I30" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -5214,19 +5212,19 @@
         <v>114</v>
       </c>
       <c r="E31">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F31">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G31" s="1">
-        <v>77.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H31" s="1">
-        <v>22.8</v>
+        <v>18.4</v>
       </c>
       <c r="I31" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -5249,19 +5247,19 @@
         <v>21</v>
       </c>
       <c r="E32">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G32" s="1">
-        <v>52.4</v>
+        <v>61.9</v>
       </c>
       <c r="H32" s="1">
-        <v>47.6</v>
+        <v>38.1</v>
       </c>
       <c r="I32" s="2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -5284,19 +5282,19 @@
         <v>19</v>
       </c>
       <c r="E33">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F33">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G33" s="1">
-        <v>57.9</v>
+        <v>89.5</v>
       </c>
       <c r="H33" s="1">
-        <v>42.1</v>
+        <v>10.5</v>
       </c>
       <c r="I33" s="2">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -5316,19 +5314,19 @@
         <v>40</v>
       </c>
       <c r="E34">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F34">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G34" s="1">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H34" s="1">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="I34" s="2">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -5625,19 +5623,19 @@
         <v>30</v>
       </c>
       <c r="E43">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F43">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H43" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I43" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -5695,19 +5693,19 @@
         <v>20</v>
       </c>
       <c r="E45">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G45" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H45" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I45" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -5730,19 +5728,19 @@
         <v>28</v>
       </c>
       <c r="E46">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F46">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G46" s="1">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H46" s="1">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I46" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -5762,19 +5760,19 @@
         <v>144</v>
       </c>
       <c r="E47">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="F47">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="G47" s="1">
-        <v>84</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H47" s="1">
-        <v>16</v>
+        <v>4.9</v>
       </c>
       <c r="I47" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -5928,16 +5926,16 @@
         <v>1174</v>
       </c>
       <c r="E52">
-        <v>860</v>
+        <v>920</v>
       </c>
       <c r="F52">
-        <v>314</v>
+        <v>254</v>
       </c>
       <c r="G52" s="1">
-        <v>73.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H52" s="1">
-        <v>26.7</v>
+        <v>21.6</v>
       </c>
       <c r="I52" s="2">
         <v>7</v>

--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -5521,19 +5521,19 @@
         <v>17</v>
       </c>
       <c r="E40">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G40" s="1">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="H40" s="1">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="I40" s="2">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -5553,19 +5553,19 @@
         <v>17</v>
       </c>
       <c r="E41">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="1">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="H41" s="1">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="I41" s="2">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -5926,16 +5926,16 @@
         <v>1174</v>
       </c>
       <c r="E52">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="F52">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G52" s="1">
-        <v>78.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="H52" s="1">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="I52" s="2">
         <v>7</v>

--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -4422,16 +4422,16 @@
         <v>37</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G8" s="1">
-        <v>59.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>40.5</v>
+        <v>32.4</v>
       </c>
       <c r="I8" s="2">
         <v>6.4</v>
@@ -4457,19 +4457,19 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F9">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G9" s="1">
-        <v>35.5</v>
+        <v>51.6</v>
       </c>
       <c r="H9" s="1">
-        <v>64.5</v>
+        <v>48.4</v>
       </c>
       <c r="I9" s="2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -4492,19 +4492,19 @@
         <v>41</v>
       </c>
       <c r="E10">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1">
-        <v>46.3</v>
+        <v>58.5</v>
       </c>
       <c r="H10" s="1">
-        <v>53.7</v>
+        <v>41.5</v>
       </c>
       <c r="I10" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -4527,19 +4527,19 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F11">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>54.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>45.2</v>
+        <v>19.4</v>
       </c>
       <c r="I11" s="2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -4562,19 +4562,19 @@
         <v>38</v>
       </c>
       <c r="E12">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>86.8</v>
+        <v>84.2</v>
       </c>
       <c r="H12" s="1">
-        <v>13.2</v>
+        <v>15.8</v>
       </c>
       <c r="I12" s="2">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -4597,19 +4597,19 @@
         <v>28</v>
       </c>
       <c r="E13">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>64.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>35.7</v>
+        <v>21.4</v>
       </c>
       <c r="I13" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -4632,19 +4632,19 @@
         <v>41</v>
       </c>
       <c r="E14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1">
-        <v>58.5</v>
+        <v>73.2</v>
       </c>
       <c r="H14" s="1">
-        <v>41.5</v>
+        <v>26.8</v>
       </c>
       <c r="I14" s="2">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -4664,19 +4664,19 @@
         <v>247</v>
       </c>
       <c r="E15">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="F15">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="G15" s="1">
-        <v>58.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>41.7</v>
+        <v>29.6</v>
       </c>
       <c r="I15" s="2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -5588,16 +5588,16 @@
         <v>32</v>
       </c>
       <c r="E42">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G42" s="1">
-        <v>78.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="H42" s="1">
-        <v>21.9</v>
+        <v>18.8</v>
       </c>
       <c r="I42" s="2">
         <v>6.8</v>
@@ -5760,16 +5760,16 @@
         <v>144</v>
       </c>
       <c r="E47">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F47">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G47" s="1">
-        <v>95.09999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="H47" s="1">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="I47" s="2">
         <v>7.4</v>
@@ -5926,16 +5926,16 @@
         <v>1174</v>
       </c>
       <c r="E52">
-        <v>918</v>
+        <v>949</v>
       </c>
       <c r="F52">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="G52" s="1">
-        <v>78.2</v>
+        <v>80.8</v>
       </c>
       <c r="H52" s="1">
-        <v>21.8</v>
+        <v>19.2</v>
       </c>
       <c r="I52" s="2">
         <v>7</v>

--- a/academias/Matemáticas - Estadisticos 20222.xlsx
+++ b/academias/Matemáticas - Estadisticos 20222.xlsx
@@ -5349,19 +5349,19 @@
         <v>34</v>
       </c>
       <c r="E35">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F35">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G35" s="1">
-        <v>79.40000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H35" s="1">
-        <v>20.6</v>
+        <v>32.4</v>
       </c>
       <c r="I35" s="2">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -5396,7 +5396,7 @@
         <v>18.6</v>
       </c>
       <c r="I36" s="2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -5419,19 +5419,19 @@
         <v>40</v>
       </c>
       <c r="E37">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F37">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G37" s="1">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H37" s="1">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I37" s="2">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -5454,19 +5454,19 @@
         <v>42</v>
       </c>
       <c r="E38">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F38">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G38" s="1">
-        <v>71.40000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="H38" s="1">
-        <v>28.6</v>
+        <v>38.1</v>
       </c>
       <c r="I38" s="2">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -5486,19 +5486,19 @@
         <v>159</v>
       </c>
       <c r="E39">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="F39">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G39" s="1">
-        <v>75.5</v>
+        <v>66.7</v>
       </c>
       <c r="H39" s="1">
-        <v>24.5</v>
+        <v>33.3</v>
       </c>
       <c r="I39" s="2">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -5795,19 +5795,19 @@
         <v>30</v>
       </c>
       <c r="E48">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F48">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G48" s="1">
-        <v>36.7</v>
+        <v>73.3</v>
       </c>
       <c r="H48" s="1">
-        <v>63.3</v>
+        <v>26.7</v>
       </c>
       <c r="I48" s="2">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -5830,19 +5830,19 @@
         <v>34</v>
       </c>
       <c r="E49">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F49">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G49" s="1">
-        <v>76.5</v>
+        <v>88.2</v>
       </c>
       <c r="H49" s="1">
-        <v>23.5</v>
+        <v>11.8</v>
       </c>
       <c r="I49" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -5865,19 +5865,19 @@
         <v>33</v>
       </c>
       <c r="E50">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F50">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G50" s="1">
-        <v>63.6</v>
+        <v>84.8</v>
       </c>
       <c r="H50" s="1">
-        <v>36.4</v>
+        <v>15.2</v>
       </c>
       <c r="I50" s="2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -5897,19 +5897,19 @@
         <v>97</v>
       </c>
       <c r="E51">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F51">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G51" s="1">
-        <v>59.8</v>
+        <v>82.5</v>
       </c>
       <c r="H51" s="1">
-        <v>40.2</v>
+        <v>17.5</v>
       </c>
       <c r="I51" s="2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -5926,16 +5926,16 @@
         <v>1174</v>
       </c>
       <c r="E52">
-        <v>949</v>
+        <v>957</v>
       </c>
       <c r="F52">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="G52" s="1">
-        <v>80.8</v>
+        <v>81.5</v>
       </c>
       <c r="H52" s="1">
-        <v>19.2</v>
+        <v>18.5</v>
       </c>
       <c r="I52" s="2">
         <v>7</v>
